--- a/MedPlus_1000_User_Load_Test_Report.xlsx
+++ b/MedPlus_1000_User_Load_Test_Report.xlsx
@@ -21,7 +21,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
-  <fonts count="13">
+  <fonts count="12">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -88,11 +88,6 @@
       <b val="1"/>
       <color rgb="001B5E20"/>
       <sz val="9"/>
-    </font>
-    <font>
-      <name val="Segoe UI"/>
-      <i val="1"/>
-      <sz val="11"/>
     </font>
   </fonts>
   <fills count="6">
@@ -172,7 +167,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -216,7 +211,12 @@
     <xf numFmtId="0" fontId="11" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="10" fontId="9" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1212,14 +1212,3887 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:I99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="11" customWidth="1" min="1" max="1"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="39" customWidth="1" min="5" max="5"/>
+    <col width="17" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="17" customWidth="1" min="9" max="9"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="21" t="inlineStr">
-        <is>
-          <t>Percentile response latencies and ramping progression log.</t>
-        </is>
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>VU Tier</t>
+        </is>
+      </c>
+      <c r="B1" s="5" t="inlineStr">
+        <is>
+          <t>Module Scenario ID</t>
+        </is>
+      </c>
+      <c r="C1" s="21" t="inlineStr">
+        <is>
+          <t>Scenario Module Name</t>
+        </is>
+      </c>
+      <c r="D1" s="21" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="E1" s="21" t="inlineStr">
+        <is>
+          <t>Endpoint</t>
+        </is>
+      </c>
+      <c r="F1" s="5" t="inlineStr">
+        <is>
+          <t>Total Requests</t>
+        </is>
+      </c>
+      <c r="G1" s="5" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="H1" s="5" t="inlineStr">
+        <is>
+          <t>Failed</t>
+        </is>
+      </c>
+      <c r="I1" s="5" t="inlineStr">
+        <is>
+          <t>Error Rate (%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="13" t="inlineStr">
+        <is>
+          <t>10 VUs</t>
+        </is>
+      </c>
+      <c r="B2" s="13" t="inlineStr">
+        <is>
+          <t>S01</t>
+        </is>
+      </c>
+      <c r="C2" s="12" t="inlineStr">
+        <is>
+          <t>User Login</t>
+        </is>
+      </c>
+      <c r="D2" s="12" t="inlineStr">
+        <is>
+          <t>Authentication</t>
+        </is>
+      </c>
+      <c r="E2" s="12" t="inlineStr">
+        <is>
+          <t>/api/auth/login</t>
+        </is>
+      </c>
+      <c r="F2" s="13" t="n">
+        <v>10</v>
+      </c>
+      <c r="G2" s="13" t="n">
+        <v>10</v>
+      </c>
+      <c r="H2" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" s="22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>10 VUs</t>
+        </is>
+      </c>
+      <c r="B3" s="13" t="inlineStr">
+        <is>
+          <t>S02</t>
+        </is>
+      </c>
+      <c r="C3" s="12" t="inlineStr">
+        <is>
+          <t>User Registration</t>
+        </is>
+      </c>
+      <c r="D3" s="12" t="inlineStr">
+        <is>
+          <t>Authentication</t>
+        </is>
+      </c>
+      <c r="E3" s="12" t="inlineStr">
+        <is>
+          <t>/api/auth/register</t>
+        </is>
+      </c>
+      <c r="F3" s="13" t="n">
+        <v>10</v>
+      </c>
+      <c r="G3" s="13" t="n">
+        <v>10</v>
+      </c>
+      <c r="H3" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" s="22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="13" t="inlineStr">
+        <is>
+          <t>10 VUs</t>
+        </is>
+      </c>
+      <c r="B4" s="13" t="inlineStr">
+        <is>
+          <t>S03</t>
+        </is>
+      </c>
+      <c r="C4" s="12" t="inlineStr">
+        <is>
+          <t>Update Doctor Profile</t>
+        </is>
+      </c>
+      <c r="D4" s="12" t="inlineStr">
+        <is>
+          <t>Doctor Portal</t>
+        </is>
+      </c>
+      <c r="E4" s="12" t="inlineStr">
+        <is>
+          <t>/api/doctors/:id/profile</t>
+        </is>
+      </c>
+      <c r="F4" s="13" t="n">
+        <v>10</v>
+      </c>
+      <c r="G4" s="13" t="n">
+        <v>10</v>
+      </c>
+      <c r="H4" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" s="22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="13" t="inlineStr">
+        <is>
+          <t>10 VUs</t>
+        </is>
+      </c>
+      <c r="B5" s="13" t="inlineStr">
+        <is>
+          <t>S04</t>
+        </is>
+      </c>
+      <c r="C5" s="12" t="inlineStr">
+        <is>
+          <t>Book Appointment</t>
+        </is>
+      </c>
+      <c r="D5" s="12" t="inlineStr">
+        <is>
+          <t>Booking Engine</t>
+        </is>
+      </c>
+      <c r="E5" s="12" t="inlineStr">
+        <is>
+          <t>/api/appointments</t>
+        </is>
+      </c>
+      <c r="F5" s="13" t="n">
+        <v>10</v>
+      </c>
+      <c r="G5" s="13" t="n">
+        <v>10</v>
+      </c>
+      <c r="H5" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" s="22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="13" t="inlineStr">
+        <is>
+          <t>10 VUs</t>
+        </is>
+      </c>
+      <c r="B6" s="13" t="inlineStr">
+        <is>
+          <t>S05</t>
+        </is>
+      </c>
+      <c r="C6" s="12" t="inlineStr">
+        <is>
+          <t>Patient Appointments List</t>
+        </is>
+      </c>
+      <c r="D6" s="12" t="inlineStr">
+        <is>
+          <t>Booking Engine</t>
+        </is>
+      </c>
+      <c r="E6" s="12" t="inlineStr">
+        <is>
+          <t>/api/appointments/patient/:patientId</t>
+        </is>
+      </c>
+      <c r="F6" s="13" t="n">
+        <v>10</v>
+      </c>
+      <c r="G6" s="13" t="n">
+        <v>10</v>
+      </c>
+      <c r="H6" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" s="22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="13" t="inlineStr">
+        <is>
+          <t>10 VUs</t>
+        </is>
+      </c>
+      <c r="B7" s="13" t="inlineStr">
+        <is>
+          <t>S06</t>
+        </is>
+      </c>
+      <c r="C7" s="12" t="inlineStr">
+        <is>
+          <t>Doctor Appointments List</t>
+        </is>
+      </c>
+      <c r="D7" s="12" t="inlineStr">
+        <is>
+          <t>Booking Engine</t>
+        </is>
+      </c>
+      <c r="E7" s="12" t="inlineStr">
+        <is>
+          <t>/api/appointments/doctor/:doctorId</t>
+        </is>
+      </c>
+      <c r="F7" s="13" t="n">
+        <v>10</v>
+      </c>
+      <c r="G7" s="13" t="n">
+        <v>10</v>
+      </c>
+      <c r="H7" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" s="22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="13" t="inlineStr">
+        <is>
+          <t>10 VUs</t>
+        </is>
+      </c>
+      <c r="B8" s="13" t="inlineStr">
+        <is>
+          <t>S07</t>
+        </is>
+      </c>
+      <c r="C8" s="12" t="inlineStr">
+        <is>
+          <t>Get Appointment Details</t>
+        </is>
+      </c>
+      <c r="D8" s="12" t="inlineStr">
+        <is>
+          <t>Booking Engine</t>
+        </is>
+      </c>
+      <c r="E8" s="12" t="inlineStr">
+        <is>
+          <t>/api/appointments/:id</t>
+        </is>
+      </c>
+      <c r="F8" s="13" t="n">
+        <v>10</v>
+      </c>
+      <c r="G8" s="13" t="n">
+        <v>10</v>
+      </c>
+      <c r="H8" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" s="22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="13" t="inlineStr">
+        <is>
+          <t>10 VUs</t>
+        </is>
+      </c>
+      <c r="B9" s="13" t="inlineStr">
+        <is>
+          <t>S08</t>
+        </is>
+      </c>
+      <c r="C9" s="12" t="inlineStr">
+        <is>
+          <t>Queue Registration</t>
+        </is>
+      </c>
+      <c r="D9" s="12" t="inlineStr">
+        <is>
+          <t>Queue Manager</t>
+        </is>
+      </c>
+      <c r="E9" s="12" t="inlineStr">
+        <is>
+          <t>/api/queue</t>
+        </is>
+      </c>
+      <c r="F9" s="13" t="n">
+        <v>10</v>
+      </c>
+      <c r="G9" s="13" t="n">
+        <v>10</v>
+      </c>
+      <c r="H9" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" s="22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="13" t="inlineStr">
+        <is>
+          <t>10 VUs</t>
+        </is>
+      </c>
+      <c r="B10" s="13" t="inlineStr">
+        <is>
+          <t>S09</t>
+        </is>
+      </c>
+      <c r="C10" s="12" t="inlineStr">
+        <is>
+          <t>Update Queue Status</t>
+        </is>
+      </c>
+      <c r="D10" s="12" t="inlineStr">
+        <is>
+          <t>Queue Manager</t>
+        </is>
+      </c>
+      <c r="E10" s="12" t="inlineStr">
+        <is>
+          <t>/api/queue/:id/status</t>
+        </is>
+      </c>
+      <c r="F10" s="13" t="n">
+        <v>10</v>
+      </c>
+      <c r="G10" s="13" t="n">
+        <v>10</v>
+      </c>
+      <c r="H10" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" s="22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="13" t="inlineStr">
+        <is>
+          <t>10 VUs</t>
+        </is>
+      </c>
+      <c r="B11" s="13" t="inlineStr">
+        <is>
+          <t>S10</t>
+        </is>
+      </c>
+      <c r="C11" s="12" t="inlineStr">
+        <is>
+          <t>Fetch Notifications</t>
+        </is>
+      </c>
+      <c r="D11" s="12" t="inlineStr">
+        <is>
+          <t>Notification Engine</t>
+        </is>
+      </c>
+      <c r="E11" s="12" t="inlineStr">
+        <is>
+          <t>/api/notifications/:userId</t>
+        </is>
+      </c>
+      <c r="F11" s="13" t="n">
+        <v>10</v>
+      </c>
+      <c r="G11" s="13" t="n">
+        <v>10</v>
+      </c>
+      <c r="H11" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" s="22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="13" t="inlineStr">
+        <is>
+          <t>10 VUs</t>
+        </is>
+      </c>
+      <c r="B12" s="13" t="inlineStr">
+        <is>
+          <t>S11</t>
+        </is>
+      </c>
+      <c r="C12" s="12" t="inlineStr">
+        <is>
+          <t>Submit Feedback</t>
+        </is>
+      </c>
+      <c r="D12" s="12" t="inlineStr">
+        <is>
+          <t>Feedback System</t>
+        </is>
+      </c>
+      <c r="E12" s="12" t="inlineStr">
+        <is>
+          <t>/api/feedback</t>
+        </is>
+      </c>
+      <c r="F12" s="13" t="n">
+        <v>10</v>
+      </c>
+      <c r="G12" s="13" t="n">
+        <v>10</v>
+      </c>
+      <c r="H12" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" s="22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="13" t="inlineStr">
+        <is>
+          <t>10 VUs</t>
+        </is>
+      </c>
+      <c r="B13" s="13" t="inlineStr">
+        <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="C13" s="12" t="inlineStr">
+        <is>
+          <t>Upload Medical Record</t>
+        </is>
+      </c>
+      <c r="D13" s="12" t="inlineStr">
+        <is>
+          <t>Medical Records</t>
+        </is>
+      </c>
+      <c r="E13" s="12" t="inlineStr">
+        <is>
+          <t>/api/medical-records</t>
+        </is>
+      </c>
+      <c r="F13" s="13" t="n">
+        <v>10</v>
+      </c>
+      <c r="G13" s="13" t="n">
+        <v>10</v>
+      </c>
+      <c r="H13" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" s="22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="13" t="inlineStr">
+        <is>
+          <t>10 VUs</t>
+        </is>
+      </c>
+      <c r="B14" s="13" t="inlineStr">
+        <is>
+          <t>S13</t>
+        </is>
+      </c>
+      <c r="C14" s="12" t="inlineStr">
+        <is>
+          <t>Patient Dashboard Loading</t>
+        </is>
+      </c>
+      <c r="D14" s="12" t="inlineStr">
+        <is>
+          <t>User Dashboard</t>
+        </is>
+      </c>
+      <c r="E14" s="12" t="inlineStr">
+        <is>
+          <t>/api/dashboard/patient/:patientId</t>
+        </is>
+      </c>
+      <c r="F14" s="13" t="n">
+        <v>10</v>
+      </c>
+      <c r="G14" s="13" t="n">
+        <v>10</v>
+      </c>
+      <c r="H14" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" s="22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="13" t="inlineStr">
+        <is>
+          <t>10 VUs</t>
+        </is>
+      </c>
+      <c r="B15" s="13" t="inlineStr">
+        <is>
+          <t>S14</t>
+        </is>
+      </c>
+      <c r="C15" s="12" t="inlineStr">
+        <is>
+          <t>Doctor Dashboard Loading</t>
+        </is>
+      </c>
+      <c r="D15" s="12" t="inlineStr">
+        <is>
+          <t>User Dashboard</t>
+        </is>
+      </c>
+      <c r="E15" s="12" t="inlineStr">
+        <is>
+          <t>/api/dashboard/doctor/:doctorId</t>
+        </is>
+      </c>
+      <c r="F15" s="13" t="n">
+        <v>10</v>
+      </c>
+      <c r="G15" s="13" t="n">
+        <v>10</v>
+      </c>
+      <c r="H15" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" s="22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="13" t="inlineStr">
+        <is>
+          <t>25 VUs</t>
+        </is>
+      </c>
+      <c r="B16" s="13" t="inlineStr">
+        <is>
+          <t>S01</t>
+        </is>
+      </c>
+      <c r="C16" s="12" t="inlineStr">
+        <is>
+          <t>User Login</t>
+        </is>
+      </c>
+      <c r="D16" s="12" t="inlineStr">
+        <is>
+          <t>Authentication</t>
+        </is>
+      </c>
+      <c r="E16" s="12" t="inlineStr">
+        <is>
+          <t>/api/auth/login</t>
+        </is>
+      </c>
+      <c r="F16" s="13" t="n">
+        <v>25</v>
+      </c>
+      <c r="G16" s="13" t="n">
+        <v>25</v>
+      </c>
+      <c r="H16" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" s="22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="13" t="inlineStr">
+        <is>
+          <t>25 VUs</t>
+        </is>
+      </c>
+      <c r="B17" s="13" t="inlineStr">
+        <is>
+          <t>S02</t>
+        </is>
+      </c>
+      <c r="C17" s="12" t="inlineStr">
+        <is>
+          <t>User Registration</t>
+        </is>
+      </c>
+      <c r="D17" s="12" t="inlineStr">
+        <is>
+          <t>Authentication</t>
+        </is>
+      </c>
+      <c r="E17" s="12" t="inlineStr">
+        <is>
+          <t>/api/auth/register</t>
+        </is>
+      </c>
+      <c r="F17" s="13" t="n">
+        <v>25</v>
+      </c>
+      <c r="G17" s="13" t="n">
+        <v>25</v>
+      </c>
+      <c r="H17" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" s="22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="13" t="inlineStr">
+        <is>
+          <t>25 VUs</t>
+        </is>
+      </c>
+      <c r="B18" s="13" t="inlineStr">
+        <is>
+          <t>S03</t>
+        </is>
+      </c>
+      <c r="C18" s="12" t="inlineStr">
+        <is>
+          <t>Update Doctor Profile</t>
+        </is>
+      </c>
+      <c r="D18" s="12" t="inlineStr">
+        <is>
+          <t>Doctor Portal</t>
+        </is>
+      </c>
+      <c r="E18" s="12" t="inlineStr">
+        <is>
+          <t>/api/doctors/:id/profile</t>
+        </is>
+      </c>
+      <c r="F18" s="13" t="n">
+        <v>25</v>
+      </c>
+      <c r="G18" s="13" t="n">
+        <v>25</v>
+      </c>
+      <c r="H18" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" s="22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="13" t="inlineStr">
+        <is>
+          <t>25 VUs</t>
+        </is>
+      </c>
+      <c r="B19" s="13" t="inlineStr">
+        <is>
+          <t>S04</t>
+        </is>
+      </c>
+      <c r="C19" s="12" t="inlineStr">
+        <is>
+          <t>Book Appointment</t>
+        </is>
+      </c>
+      <c r="D19" s="12" t="inlineStr">
+        <is>
+          <t>Booking Engine</t>
+        </is>
+      </c>
+      <c r="E19" s="12" t="inlineStr">
+        <is>
+          <t>/api/appointments</t>
+        </is>
+      </c>
+      <c r="F19" s="13" t="n">
+        <v>25</v>
+      </c>
+      <c r="G19" s="13" t="n">
+        <v>25</v>
+      </c>
+      <c r="H19" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" s="22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="13" t="inlineStr">
+        <is>
+          <t>25 VUs</t>
+        </is>
+      </c>
+      <c r="B20" s="13" t="inlineStr">
+        <is>
+          <t>S05</t>
+        </is>
+      </c>
+      <c r="C20" s="12" t="inlineStr">
+        <is>
+          <t>Patient Appointments List</t>
+        </is>
+      </c>
+      <c r="D20" s="12" t="inlineStr">
+        <is>
+          <t>Booking Engine</t>
+        </is>
+      </c>
+      <c r="E20" s="12" t="inlineStr">
+        <is>
+          <t>/api/appointments/patient/:patientId</t>
+        </is>
+      </c>
+      <c r="F20" s="13" t="n">
+        <v>25</v>
+      </c>
+      <c r="G20" s="13" t="n">
+        <v>25</v>
+      </c>
+      <c r="H20" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" s="22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="13" t="inlineStr">
+        <is>
+          <t>25 VUs</t>
+        </is>
+      </c>
+      <c r="B21" s="13" t="inlineStr">
+        <is>
+          <t>S06</t>
+        </is>
+      </c>
+      <c r="C21" s="12" t="inlineStr">
+        <is>
+          <t>Doctor Appointments List</t>
+        </is>
+      </c>
+      <c r="D21" s="12" t="inlineStr">
+        <is>
+          <t>Booking Engine</t>
+        </is>
+      </c>
+      <c r="E21" s="12" t="inlineStr">
+        <is>
+          <t>/api/appointments/doctor/:doctorId</t>
+        </is>
+      </c>
+      <c r="F21" s="13" t="n">
+        <v>25</v>
+      </c>
+      <c r="G21" s="13" t="n">
+        <v>25</v>
+      </c>
+      <c r="H21" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" s="22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="13" t="inlineStr">
+        <is>
+          <t>25 VUs</t>
+        </is>
+      </c>
+      <c r="B22" s="13" t="inlineStr">
+        <is>
+          <t>S07</t>
+        </is>
+      </c>
+      <c r="C22" s="12" t="inlineStr">
+        <is>
+          <t>Get Appointment Details</t>
+        </is>
+      </c>
+      <c r="D22" s="12" t="inlineStr">
+        <is>
+          <t>Booking Engine</t>
+        </is>
+      </c>
+      <c r="E22" s="12" t="inlineStr">
+        <is>
+          <t>/api/appointments/:id</t>
+        </is>
+      </c>
+      <c r="F22" s="13" t="n">
+        <v>25</v>
+      </c>
+      <c r="G22" s="13" t="n">
+        <v>25</v>
+      </c>
+      <c r="H22" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" s="22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="13" t="inlineStr">
+        <is>
+          <t>25 VUs</t>
+        </is>
+      </c>
+      <c r="B23" s="13" t="inlineStr">
+        <is>
+          <t>S08</t>
+        </is>
+      </c>
+      <c r="C23" s="12" t="inlineStr">
+        <is>
+          <t>Queue Registration</t>
+        </is>
+      </c>
+      <c r="D23" s="12" t="inlineStr">
+        <is>
+          <t>Queue Manager</t>
+        </is>
+      </c>
+      <c r="E23" s="12" t="inlineStr">
+        <is>
+          <t>/api/queue</t>
+        </is>
+      </c>
+      <c r="F23" s="13" t="n">
+        <v>25</v>
+      </c>
+      <c r="G23" s="13" t="n">
+        <v>25</v>
+      </c>
+      <c r="H23" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" s="22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="13" t="inlineStr">
+        <is>
+          <t>25 VUs</t>
+        </is>
+      </c>
+      <c r="B24" s="13" t="inlineStr">
+        <is>
+          <t>S09</t>
+        </is>
+      </c>
+      <c r="C24" s="12" t="inlineStr">
+        <is>
+          <t>Update Queue Status</t>
+        </is>
+      </c>
+      <c r="D24" s="12" t="inlineStr">
+        <is>
+          <t>Queue Manager</t>
+        </is>
+      </c>
+      <c r="E24" s="12" t="inlineStr">
+        <is>
+          <t>/api/queue/:id/status</t>
+        </is>
+      </c>
+      <c r="F24" s="13" t="n">
+        <v>25</v>
+      </c>
+      <c r="G24" s="13" t="n">
+        <v>25</v>
+      </c>
+      <c r="H24" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" s="22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="13" t="inlineStr">
+        <is>
+          <t>25 VUs</t>
+        </is>
+      </c>
+      <c r="B25" s="13" t="inlineStr">
+        <is>
+          <t>S10</t>
+        </is>
+      </c>
+      <c r="C25" s="12" t="inlineStr">
+        <is>
+          <t>Fetch Notifications</t>
+        </is>
+      </c>
+      <c r="D25" s="12" t="inlineStr">
+        <is>
+          <t>Notification Engine</t>
+        </is>
+      </c>
+      <c r="E25" s="12" t="inlineStr">
+        <is>
+          <t>/api/notifications/:userId</t>
+        </is>
+      </c>
+      <c r="F25" s="13" t="n">
+        <v>25</v>
+      </c>
+      <c r="G25" s="13" t="n">
+        <v>25</v>
+      </c>
+      <c r="H25" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" s="22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="13" t="inlineStr">
+        <is>
+          <t>25 VUs</t>
+        </is>
+      </c>
+      <c r="B26" s="13" t="inlineStr">
+        <is>
+          <t>S11</t>
+        </is>
+      </c>
+      <c r="C26" s="12" t="inlineStr">
+        <is>
+          <t>Submit Feedback</t>
+        </is>
+      </c>
+      <c r="D26" s="12" t="inlineStr">
+        <is>
+          <t>Feedback System</t>
+        </is>
+      </c>
+      <c r="E26" s="12" t="inlineStr">
+        <is>
+          <t>/api/feedback</t>
+        </is>
+      </c>
+      <c r="F26" s="13" t="n">
+        <v>25</v>
+      </c>
+      <c r="G26" s="13" t="n">
+        <v>25</v>
+      </c>
+      <c r="H26" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" s="22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="13" t="inlineStr">
+        <is>
+          <t>25 VUs</t>
+        </is>
+      </c>
+      <c r="B27" s="13" t="inlineStr">
+        <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="C27" s="12" t="inlineStr">
+        <is>
+          <t>Upload Medical Record</t>
+        </is>
+      </c>
+      <c r="D27" s="12" t="inlineStr">
+        <is>
+          <t>Medical Records</t>
+        </is>
+      </c>
+      <c r="E27" s="12" t="inlineStr">
+        <is>
+          <t>/api/medical-records</t>
+        </is>
+      </c>
+      <c r="F27" s="13" t="n">
+        <v>25</v>
+      </c>
+      <c r="G27" s="13" t="n">
+        <v>25</v>
+      </c>
+      <c r="H27" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" s="22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="13" t="inlineStr">
+        <is>
+          <t>25 VUs</t>
+        </is>
+      </c>
+      <c r="B28" s="13" t="inlineStr">
+        <is>
+          <t>S13</t>
+        </is>
+      </c>
+      <c r="C28" s="12" t="inlineStr">
+        <is>
+          <t>Patient Dashboard Loading</t>
+        </is>
+      </c>
+      <c r="D28" s="12" t="inlineStr">
+        <is>
+          <t>User Dashboard</t>
+        </is>
+      </c>
+      <c r="E28" s="12" t="inlineStr">
+        <is>
+          <t>/api/dashboard/patient/:patientId</t>
+        </is>
+      </c>
+      <c r="F28" s="13" t="n">
+        <v>25</v>
+      </c>
+      <c r="G28" s="13" t="n">
+        <v>25</v>
+      </c>
+      <c r="H28" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I28" s="22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="13" t="inlineStr">
+        <is>
+          <t>25 VUs</t>
+        </is>
+      </c>
+      <c r="B29" s="13" t="inlineStr">
+        <is>
+          <t>S14</t>
+        </is>
+      </c>
+      <c r="C29" s="12" t="inlineStr">
+        <is>
+          <t>Doctor Dashboard Loading</t>
+        </is>
+      </c>
+      <c r="D29" s="12" t="inlineStr">
+        <is>
+          <t>User Dashboard</t>
+        </is>
+      </c>
+      <c r="E29" s="12" t="inlineStr">
+        <is>
+          <t>/api/dashboard/doctor/:doctorId</t>
+        </is>
+      </c>
+      <c r="F29" s="13" t="n">
+        <v>25</v>
+      </c>
+      <c r="G29" s="13" t="n">
+        <v>25</v>
+      </c>
+      <c r="H29" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I29" s="22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="13" t="inlineStr">
+        <is>
+          <t>50 VUs</t>
+        </is>
+      </c>
+      <c r="B30" s="13" t="inlineStr">
+        <is>
+          <t>S01</t>
+        </is>
+      </c>
+      <c r="C30" s="12" t="inlineStr">
+        <is>
+          <t>User Login</t>
+        </is>
+      </c>
+      <c r="D30" s="12" t="inlineStr">
+        <is>
+          <t>Authentication</t>
+        </is>
+      </c>
+      <c r="E30" s="12" t="inlineStr">
+        <is>
+          <t>/api/auth/login</t>
+        </is>
+      </c>
+      <c r="F30" s="13" t="n">
+        <v>50</v>
+      </c>
+      <c r="G30" s="13" t="n">
+        <v>50</v>
+      </c>
+      <c r="H30" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" s="22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="13" t="inlineStr">
+        <is>
+          <t>50 VUs</t>
+        </is>
+      </c>
+      <c r="B31" s="13" t="inlineStr">
+        <is>
+          <t>S02</t>
+        </is>
+      </c>
+      <c r="C31" s="12" t="inlineStr">
+        <is>
+          <t>User Registration</t>
+        </is>
+      </c>
+      <c r="D31" s="12" t="inlineStr">
+        <is>
+          <t>Authentication</t>
+        </is>
+      </c>
+      <c r="E31" s="12" t="inlineStr">
+        <is>
+          <t>/api/auth/register</t>
+        </is>
+      </c>
+      <c r="F31" s="13" t="n">
+        <v>50</v>
+      </c>
+      <c r="G31" s="13" t="n">
+        <v>50</v>
+      </c>
+      <c r="H31" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I31" s="22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="13" t="inlineStr">
+        <is>
+          <t>50 VUs</t>
+        </is>
+      </c>
+      <c r="B32" s="13" t="inlineStr">
+        <is>
+          <t>S03</t>
+        </is>
+      </c>
+      <c r="C32" s="12" t="inlineStr">
+        <is>
+          <t>Update Doctor Profile</t>
+        </is>
+      </c>
+      <c r="D32" s="12" t="inlineStr">
+        <is>
+          <t>Doctor Portal</t>
+        </is>
+      </c>
+      <c r="E32" s="12" t="inlineStr">
+        <is>
+          <t>/api/doctors/:id/profile</t>
+        </is>
+      </c>
+      <c r="F32" s="13" t="n">
+        <v>50</v>
+      </c>
+      <c r="G32" s="13" t="n">
+        <v>50</v>
+      </c>
+      <c r="H32" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I32" s="22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="13" t="inlineStr">
+        <is>
+          <t>50 VUs</t>
+        </is>
+      </c>
+      <c r="B33" s="13" t="inlineStr">
+        <is>
+          <t>S04</t>
+        </is>
+      </c>
+      <c r="C33" s="12" t="inlineStr">
+        <is>
+          <t>Book Appointment</t>
+        </is>
+      </c>
+      <c r="D33" s="12" t="inlineStr">
+        <is>
+          <t>Booking Engine</t>
+        </is>
+      </c>
+      <c r="E33" s="12" t="inlineStr">
+        <is>
+          <t>/api/appointments</t>
+        </is>
+      </c>
+      <c r="F33" s="13" t="n">
+        <v>50</v>
+      </c>
+      <c r="G33" s="13" t="n">
+        <v>50</v>
+      </c>
+      <c r="H33" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I33" s="22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="13" t="inlineStr">
+        <is>
+          <t>50 VUs</t>
+        </is>
+      </c>
+      <c r="B34" s="13" t="inlineStr">
+        <is>
+          <t>S05</t>
+        </is>
+      </c>
+      <c r="C34" s="12" t="inlineStr">
+        <is>
+          <t>Patient Appointments List</t>
+        </is>
+      </c>
+      <c r="D34" s="12" t="inlineStr">
+        <is>
+          <t>Booking Engine</t>
+        </is>
+      </c>
+      <c r="E34" s="12" t="inlineStr">
+        <is>
+          <t>/api/appointments/patient/:patientId</t>
+        </is>
+      </c>
+      <c r="F34" s="13" t="n">
+        <v>50</v>
+      </c>
+      <c r="G34" s="13" t="n">
+        <v>50</v>
+      </c>
+      <c r="H34" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I34" s="22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="13" t="inlineStr">
+        <is>
+          <t>50 VUs</t>
+        </is>
+      </c>
+      <c r="B35" s="13" t="inlineStr">
+        <is>
+          <t>S06</t>
+        </is>
+      </c>
+      <c r="C35" s="12" t="inlineStr">
+        <is>
+          <t>Doctor Appointments List</t>
+        </is>
+      </c>
+      <c r="D35" s="12" t="inlineStr">
+        <is>
+          <t>Booking Engine</t>
+        </is>
+      </c>
+      <c r="E35" s="12" t="inlineStr">
+        <is>
+          <t>/api/appointments/doctor/:doctorId</t>
+        </is>
+      </c>
+      <c r="F35" s="13" t="n">
+        <v>50</v>
+      </c>
+      <c r="G35" s="13" t="n">
+        <v>50</v>
+      </c>
+      <c r="H35" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I35" s="22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="13" t="inlineStr">
+        <is>
+          <t>50 VUs</t>
+        </is>
+      </c>
+      <c r="B36" s="13" t="inlineStr">
+        <is>
+          <t>S07</t>
+        </is>
+      </c>
+      <c r="C36" s="12" t="inlineStr">
+        <is>
+          <t>Get Appointment Details</t>
+        </is>
+      </c>
+      <c r="D36" s="12" t="inlineStr">
+        <is>
+          <t>Booking Engine</t>
+        </is>
+      </c>
+      <c r="E36" s="12" t="inlineStr">
+        <is>
+          <t>/api/appointments/:id</t>
+        </is>
+      </c>
+      <c r="F36" s="13" t="n">
+        <v>50</v>
+      </c>
+      <c r="G36" s="13" t="n">
+        <v>50</v>
+      </c>
+      <c r="H36" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I36" s="22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="13" t="inlineStr">
+        <is>
+          <t>50 VUs</t>
+        </is>
+      </c>
+      <c r="B37" s="13" t="inlineStr">
+        <is>
+          <t>S08</t>
+        </is>
+      </c>
+      <c r="C37" s="12" t="inlineStr">
+        <is>
+          <t>Queue Registration</t>
+        </is>
+      </c>
+      <c r="D37" s="12" t="inlineStr">
+        <is>
+          <t>Queue Manager</t>
+        </is>
+      </c>
+      <c r="E37" s="12" t="inlineStr">
+        <is>
+          <t>/api/queue</t>
+        </is>
+      </c>
+      <c r="F37" s="13" t="n">
+        <v>50</v>
+      </c>
+      <c r="G37" s="13" t="n">
+        <v>50</v>
+      </c>
+      <c r="H37" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I37" s="22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="13" t="inlineStr">
+        <is>
+          <t>50 VUs</t>
+        </is>
+      </c>
+      <c r="B38" s="13" t="inlineStr">
+        <is>
+          <t>S09</t>
+        </is>
+      </c>
+      <c r="C38" s="12" t="inlineStr">
+        <is>
+          <t>Update Queue Status</t>
+        </is>
+      </c>
+      <c r="D38" s="12" t="inlineStr">
+        <is>
+          <t>Queue Manager</t>
+        </is>
+      </c>
+      <c r="E38" s="12" t="inlineStr">
+        <is>
+          <t>/api/queue/:id/status</t>
+        </is>
+      </c>
+      <c r="F38" s="13" t="n">
+        <v>50</v>
+      </c>
+      <c r="G38" s="13" t="n">
+        <v>50</v>
+      </c>
+      <c r="H38" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I38" s="22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="13" t="inlineStr">
+        <is>
+          <t>50 VUs</t>
+        </is>
+      </c>
+      <c r="B39" s="13" t="inlineStr">
+        <is>
+          <t>S10</t>
+        </is>
+      </c>
+      <c r="C39" s="12" t="inlineStr">
+        <is>
+          <t>Fetch Notifications</t>
+        </is>
+      </c>
+      <c r="D39" s="12" t="inlineStr">
+        <is>
+          <t>Notification Engine</t>
+        </is>
+      </c>
+      <c r="E39" s="12" t="inlineStr">
+        <is>
+          <t>/api/notifications/:userId</t>
+        </is>
+      </c>
+      <c r="F39" s="13" t="n">
+        <v>50</v>
+      </c>
+      <c r="G39" s="13" t="n">
+        <v>50</v>
+      </c>
+      <c r="H39" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I39" s="22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="13" t="inlineStr">
+        <is>
+          <t>50 VUs</t>
+        </is>
+      </c>
+      <c r="B40" s="13" t="inlineStr">
+        <is>
+          <t>S11</t>
+        </is>
+      </c>
+      <c r="C40" s="12" t="inlineStr">
+        <is>
+          <t>Submit Feedback</t>
+        </is>
+      </c>
+      <c r="D40" s="12" t="inlineStr">
+        <is>
+          <t>Feedback System</t>
+        </is>
+      </c>
+      <c r="E40" s="12" t="inlineStr">
+        <is>
+          <t>/api/feedback</t>
+        </is>
+      </c>
+      <c r="F40" s="13" t="n">
+        <v>50</v>
+      </c>
+      <c r="G40" s="13" t="n">
+        <v>50</v>
+      </c>
+      <c r="H40" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I40" s="22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="13" t="inlineStr">
+        <is>
+          <t>50 VUs</t>
+        </is>
+      </c>
+      <c r="B41" s="13" t="inlineStr">
+        <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="C41" s="12" t="inlineStr">
+        <is>
+          <t>Upload Medical Record</t>
+        </is>
+      </c>
+      <c r="D41" s="12" t="inlineStr">
+        <is>
+          <t>Medical Records</t>
+        </is>
+      </c>
+      <c r="E41" s="12" t="inlineStr">
+        <is>
+          <t>/api/medical-records</t>
+        </is>
+      </c>
+      <c r="F41" s="13" t="n">
+        <v>50</v>
+      </c>
+      <c r="G41" s="13" t="n">
+        <v>50</v>
+      </c>
+      <c r="H41" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I41" s="22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="13" t="inlineStr">
+        <is>
+          <t>50 VUs</t>
+        </is>
+      </c>
+      <c r="B42" s="13" t="inlineStr">
+        <is>
+          <t>S13</t>
+        </is>
+      </c>
+      <c r="C42" s="12" t="inlineStr">
+        <is>
+          <t>Patient Dashboard Loading</t>
+        </is>
+      </c>
+      <c r="D42" s="12" t="inlineStr">
+        <is>
+          <t>User Dashboard</t>
+        </is>
+      </c>
+      <c r="E42" s="12" t="inlineStr">
+        <is>
+          <t>/api/dashboard/patient/:patientId</t>
+        </is>
+      </c>
+      <c r="F42" s="13" t="n">
+        <v>50</v>
+      </c>
+      <c r="G42" s="13" t="n">
+        <v>50</v>
+      </c>
+      <c r="H42" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I42" s="22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="13" t="inlineStr">
+        <is>
+          <t>50 VUs</t>
+        </is>
+      </c>
+      <c r="B43" s="13" t="inlineStr">
+        <is>
+          <t>S14</t>
+        </is>
+      </c>
+      <c r="C43" s="12" t="inlineStr">
+        <is>
+          <t>Doctor Dashboard Loading</t>
+        </is>
+      </c>
+      <c r="D43" s="12" t="inlineStr">
+        <is>
+          <t>User Dashboard</t>
+        </is>
+      </c>
+      <c r="E43" s="12" t="inlineStr">
+        <is>
+          <t>/api/dashboard/doctor/:doctorId</t>
+        </is>
+      </c>
+      <c r="F43" s="13" t="n">
+        <v>50</v>
+      </c>
+      <c r="G43" s="13" t="n">
+        <v>50</v>
+      </c>
+      <c r="H43" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I43" s="22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="13" t="inlineStr">
+        <is>
+          <t>100 VUs</t>
+        </is>
+      </c>
+      <c r="B44" s="13" t="inlineStr">
+        <is>
+          <t>S01</t>
+        </is>
+      </c>
+      <c r="C44" s="12" t="inlineStr">
+        <is>
+          <t>User Login</t>
+        </is>
+      </c>
+      <c r="D44" s="12" t="inlineStr">
+        <is>
+          <t>Authentication</t>
+        </is>
+      </c>
+      <c r="E44" s="12" t="inlineStr">
+        <is>
+          <t>/api/auth/login</t>
+        </is>
+      </c>
+      <c r="F44" s="13" t="n">
+        <v>100</v>
+      </c>
+      <c r="G44" s="13" t="n">
+        <v>100</v>
+      </c>
+      <c r="H44" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I44" s="22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="13" t="inlineStr">
+        <is>
+          <t>100 VUs</t>
+        </is>
+      </c>
+      <c r="B45" s="13" t="inlineStr">
+        <is>
+          <t>S02</t>
+        </is>
+      </c>
+      <c r="C45" s="12" t="inlineStr">
+        <is>
+          <t>User Registration</t>
+        </is>
+      </c>
+      <c r="D45" s="12" t="inlineStr">
+        <is>
+          <t>Authentication</t>
+        </is>
+      </c>
+      <c r="E45" s="12" t="inlineStr">
+        <is>
+          <t>/api/auth/register</t>
+        </is>
+      </c>
+      <c r="F45" s="13" t="n">
+        <v>100</v>
+      </c>
+      <c r="G45" s="13" t="n">
+        <v>100</v>
+      </c>
+      <c r="H45" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I45" s="22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="13" t="inlineStr">
+        <is>
+          <t>100 VUs</t>
+        </is>
+      </c>
+      <c r="B46" s="13" t="inlineStr">
+        <is>
+          <t>S03</t>
+        </is>
+      </c>
+      <c r="C46" s="12" t="inlineStr">
+        <is>
+          <t>Update Doctor Profile</t>
+        </is>
+      </c>
+      <c r="D46" s="12" t="inlineStr">
+        <is>
+          <t>Doctor Portal</t>
+        </is>
+      </c>
+      <c r="E46" s="12" t="inlineStr">
+        <is>
+          <t>/api/doctors/:id/profile</t>
+        </is>
+      </c>
+      <c r="F46" s="13" t="n">
+        <v>100</v>
+      </c>
+      <c r="G46" s="13" t="n">
+        <v>100</v>
+      </c>
+      <c r="H46" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I46" s="22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="13" t="inlineStr">
+        <is>
+          <t>100 VUs</t>
+        </is>
+      </c>
+      <c r="B47" s="13" t="inlineStr">
+        <is>
+          <t>S04</t>
+        </is>
+      </c>
+      <c r="C47" s="12" t="inlineStr">
+        <is>
+          <t>Book Appointment</t>
+        </is>
+      </c>
+      <c r="D47" s="12" t="inlineStr">
+        <is>
+          <t>Booking Engine</t>
+        </is>
+      </c>
+      <c r="E47" s="12" t="inlineStr">
+        <is>
+          <t>/api/appointments</t>
+        </is>
+      </c>
+      <c r="F47" s="13" t="n">
+        <v>100</v>
+      </c>
+      <c r="G47" s="13" t="n">
+        <v>100</v>
+      </c>
+      <c r="H47" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I47" s="22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="13" t="inlineStr">
+        <is>
+          <t>100 VUs</t>
+        </is>
+      </c>
+      <c r="B48" s="13" t="inlineStr">
+        <is>
+          <t>S05</t>
+        </is>
+      </c>
+      <c r="C48" s="12" t="inlineStr">
+        <is>
+          <t>Patient Appointments List</t>
+        </is>
+      </c>
+      <c r="D48" s="12" t="inlineStr">
+        <is>
+          <t>Booking Engine</t>
+        </is>
+      </c>
+      <c r="E48" s="12" t="inlineStr">
+        <is>
+          <t>/api/appointments/patient/:patientId</t>
+        </is>
+      </c>
+      <c r="F48" s="13" t="n">
+        <v>100</v>
+      </c>
+      <c r="G48" s="13" t="n">
+        <v>100</v>
+      </c>
+      <c r="H48" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I48" s="22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="13" t="inlineStr">
+        <is>
+          <t>100 VUs</t>
+        </is>
+      </c>
+      <c r="B49" s="13" t="inlineStr">
+        <is>
+          <t>S06</t>
+        </is>
+      </c>
+      <c r="C49" s="12" t="inlineStr">
+        <is>
+          <t>Doctor Appointments List</t>
+        </is>
+      </c>
+      <c r="D49" s="12" t="inlineStr">
+        <is>
+          <t>Booking Engine</t>
+        </is>
+      </c>
+      <c r="E49" s="12" t="inlineStr">
+        <is>
+          <t>/api/appointments/doctor/:doctorId</t>
+        </is>
+      </c>
+      <c r="F49" s="13" t="n">
+        <v>100</v>
+      </c>
+      <c r="G49" s="13" t="n">
+        <v>100</v>
+      </c>
+      <c r="H49" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I49" s="22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="13" t="inlineStr">
+        <is>
+          <t>100 VUs</t>
+        </is>
+      </c>
+      <c r="B50" s="13" t="inlineStr">
+        <is>
+          <t>S07</t>
+        </is>
+      </c>
+      <c r="C50" s="12" t="inlineStr">
+        <is>
+          <t>Get Appointment Details</t>
+        </is>
+      </c>
+      <c r="D50" s="12" t="inlineStr">
+        <is>
+          <t>Booking Engine</t>
+        </is>
+      </c>
+      <c r="E50" s="12" t="inlineStr">
+        <is>
+          <t>/api/appointments/:id</t>
+        </is>
+      </c>
+      <c r="F50" s="13" t="n">
+        <v>100</v>
+      </c>
+      <c r="G50" s="13" t="n">
+        <v>100</v>
+      </c>
+      <c r="H50" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I50" s="22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="13" t="inlineStr">
+        <is>
+          <t>100 VUs</t>
+        </is>
+      </c>
+      <c r="B51" s="13" t="inlineStr">
+        <is>
+          <t>S08</t>
+        </is>
+      </c>
+      <c r="C51" s="12" t="inlineStr">
+        <is>
+          <t>Queue Registration</t>
+        </is>
+      </c>
+      <c r="D51" s="12" t="inlineStr">
+        <is>
+          <t>Queue Manager</t>
+        </is>
+      </c>
+      <c r="E51" s="12" t="inlineStr">
+        <is>
+          <t>/api/queue</t>
+        </is>
+      </c>
+      <c r="F51" s="13" t="n">
+        <v>100</v>
+      </c>
+      <c r="G51" s="13" t="n">
+        <v>100</v>
+      </c>
+      <c r="H51" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I51" s="22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="13" t="inlineStr">
+        <is>
+          <t>100 VUs</t>
+        </is>
+      </c>
+      <c r="B52" s="13" t="inlineStr">
+        <is>
+          <t>S09</t>
+        </is>
+      </c>
+      <c r="C52" s="12" t="inlineStr">
+        <is>
+          <t>Update Queue Status</t>
+        </is>
+      </c>
+      <c r="D52" s="12" t="inlineStr">
+        <is>
+          <t>Queue Manager</t>
+        </is>
+      </c>
+      <c r="E52" s="12" t="inlineStr">
+        <is>
+          <t>/api/queue/:id/status</t>
+        </is>
+      </c>
+      <c r="F52" s="13" t="n">
+        <v>100</v>
+      </c>
+      <c r="G52" s="13" t="n">
+        <v>100</v>
+      </c>
+      <c r="H52" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I52" s="22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="13" t="inlineStr">
+        <is>
+          <t>100 VUs</t>
+        </is>
+      </c>
+      <c r="B53" s="13" t="inlineStr">
+        <is>
+          <t>S10</t>
+        </is>
+      </c>
+      <c r="C53" s="12" t="inlineStr">
+        <is>
+          <t>Fetch Notifications</t>
+        </is>
+      </c>
+      <c r="D53" s="12" t="inlineStr">
+        <is>
+          <t>Notification Engine</t>
+        </is>
+      </c>
+      <c r="E53" s="12" t="inlineStr">
+        <is>
+          <t>/api/notifications/:userId</t>
+        </is>
+      </c>
+      <c r="F53" s="13" t="n">
+        <v>100</v>
+      </c>
+      <c r="G53" s="13" t="n">
+        <v>100</v>
+      </c>
+      <c r="H53" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I53" s="22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="13" t="inlineStr">
+        <is>
+          <t>100 VUs</t>
+        </is>
+      </c>
+      <c r="B54" s="13" t="inlineStr">
+        <is>
+          <t>S11</t>
+        </is>
+      </c>
+      <c r="C54" s="12" t="inlineStr">
+        <is>
+          <t>Submit Feedback</t>
+        </is>
+      </c>
+      <c r="D54" s="12" t="inlineStr">
+        <is>
+          <t>Feedback System</t>
+        </is>
+      </c>
+      <c r="E54" s="12" t="inlineStr">
+        <is>
+          <t>/api/feedback</t>
+        </is>
+      </c>
+      <c r="F54" s="13" t="n">
+        <v>100</v>
+      </c>
+      <c r="G54" s="13" t="n">
+        <v>100</v>
+      </c>
+      <c r="H54" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I54" s="22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="13" t="inlineStr">
+        <is>
+          <t>100 VUs</t>
+        </is>
+      </c>
+      <c r="B55" s="13" t="inlineStr">
+        <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="C55" s="12" t="inlineStr">
+        <is>
+          <t>Upload Medical Record</t>
+        </is>
+      </c>
+      <c r="D55" s="12" t="inlineStr">
+        <is>
+          <t>Medical Records</t>
+        </is>
+      </c>
+      <c r="E55" s="12" t="inlineStr">
+        <is>
+          <t>/api/medical-records</t>
+        </is>
+      </c>
+      <c r="F55" s="13" t="n">
+        <v>100</v>
+      </c>
+      <c r="G55" s="13" t="n">
+        <v>100</v>
+      </c>
+      <c r="H55" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I55" s="22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="13" t="inlineStr">
+        <is>
+          <t>100 VUs</t>
+        </is>
+      </c>
+      <c r="B56" s="13" t="inlineStr">
+        <is>
+          <t>S13</t>
+        </is>
+      </c>
+      <c r="C56" s="12" t="inlineStr">
+        <is>
+          <t>Patient Dashboard Loading</t>
+        </is>
+      </c>
+      <c r="D56" s="12" t="inlineStr">
+        <is>
+          <t>User Dashboard</t>
+        </is>
+      </c>
+      <c r="E56" s="12" t="inlineStr">
+        <is>
+          <t>/api/dashboard/patient/:patientId</t>
+        </is>
+      </c>
+      <c r="F56" s="13" t="n">
+        <v>100</v>
+      </c>
+      <c r="G56" s="13" t="n">
+        <v>100</v>
+      </c>
+      <c r="H56" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I56" s="22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="13" t="inlineStr">
+        <is>
+          <t>100 VUs</t>
+        </is>
+      </c>
+      <c r="B57" s="13" t="inlineStr">
+        <is>
+          <t>S14</t>
+        </is>
+      </c>
+      <c r="C57" s="12" t="inlineStr">
+        <is>
+          <t>Doctor Dashboard Loading</t>
+        </is>
+      </c>
+      <c r="D57" s="12" t="inlineStr">
+        <is>
+          <t>User Dashboard</t>
+        </is>
+      </c>
+      <c r="E57" s="12" t="inlineStr">
+        <is>
+          <t>/api/dashboard/doctor/:doctorId</t>
+        </is>
+      </c>
+      <c r="F57" s="13" t="n">
+        <v>100</v>
+      </c>
+      <c r="G57" s="13" t="n">
+        <v>100</v>
+      </c>
+      <c r="H57" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I57" s="22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="13" t="inlineStr">
+        <is>
+          <t>250 VUs</t>
+        </is>
+      </c>
+      <c r="B58" s="13" t="inlineStr">
+        <is>
+          <t>S01</t>
+        </is>
+      </c>
+      <c r="C58" s="12" t="inlineStr">
+        <is>
+          <t>User Login</t>
+        </is>
+      </c>
+      <c r="D58" s="12" t="inlineStr">
+        <is>
+          <t>Authentication</t>
+        </is>
+      </c>
+      <c r="E58" s="12" t="inlineStr">
+        <is>
+          <t>/api/auth/login</t>
+        </is>
+      </c>
+      <c r="F58" s="13" t="n">
+        <v>250</v>
+      </c>
+      <c r="G58" s="13" t="n">
+        <v>250</v>
+      </c>
+      <c r="H58" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I58" s="22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="13" t="inlineStr">
+        <is>
+          <t>250 VUs</t>
+        </is>
+      </c>
+      <c r="B59" s="13" t="inlineStr">
+        <is>
+          <t>S02</t>
+        </is>
+      </c>
+      <c r="C59" s="12" t="inlineStr">
+        <is>
+          <t>User Registration</t>
+        </is>
+      </c>
+      <c r="D59" s="12" t="inlineStr">
+        <is>
+          <t>Authentication</t>
+        </is>
+      </c>
+      <c r="E59" s="12" t="inlineStr">
+        <is>
+          <t>/api/auth/register</t>
+        </is>
+      </c>
+      <c r="F59" s="13" t="n">
+        <v>250</v>
+      </c>
+      <c r="G59" s="13" t="n">
+        <v>250</v>
+      </c>
+      <c r="H59" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I59" s="22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="13" t="inlineStr">
+        <is>
+          <t>250 VUs</t>
+        </is>
+      </c>
+      <c r="B60" s="13" t="inlineStr">
+        <is>
+          <t>S03</t>
+        </is>
+      </c>
+      <c r="C60" s="12" t="inlineStr">
+        <is>
+          <t>Update Doctor Profile</t>
+        </is>
+      </c>
+      <c r="D60" s="12" t="inlineStr">
+        <is>
+          <t>Doctor Portal</t>
+        </is>
+      </c>
+      <c r="E60" s="12" t="inlineStr">
+        <is>
+          <t>/api/doctors/:id/profile</t>
+        </is>
+      </c>
+      <c r="F60" s="13" t="n">
+        <v>250</v>
+      </c>
+      <c r="G60" s="13" t="n">
+        <v>250</v>
+      </c>
+      <c r="H60" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I60" s="22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="13" t="inlineStr">
+        <is>
+          <t>250 VUs</t>
+        </is>
+      </c>
+      <c r="B61" s="13" t="inlineStr">
+        <is>
+          <t>S04</t>
+        </is>
+      </c>
+      <c r="C61" s="12" t="inlineStr">
+        <is>
+          <t>Book Appointment</t>
+        </is>
+      </c>
+      <c r="D61" s="12" t="inlineStr">
+        <is>
+          <t>Booking Engine</t>
+        </is>
+      </c>
+      <c r="E61" s="12" t="inlineStr">
+        <is>
+          <t>/api/appointments</t>
+        </is>
+      </c>
+      <c r="F61" s="13" t="n">
+        <v>250</v>
+      </c>
+      <c r="G61" s="13" t="n">
+        <v>250</v>
+      </c>
+      <c r="H61" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I61" s="22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="13" t="inlineStr">
+        <is>
+          <t>250 VUs</t>
+        </is>
+      </c>
+      <c r="B62" s="13" t="inlineStr">
+        <is>
+          <t>S05</t>
+        </is>
+      </c>
+      <c r="C62" s="12" t="inlineStr">
+        <is>
+          <t>Patient Appointments List</t>
+        </is>
+      </c>
+      <c r="D62" s="12" t="inlineStr">
+        <is>
+          <t>Booking Engine</t>
+        </is>
+      </c>
+      <c r="E62" s="12" t="inlineStr">
+        <is>
+          <t>/api/appointments/patient/:patientId</t>
+        </is>
+      </c>
+      <c r="F62" s="13" t="n">
+        <v>250</v>
+      </c>
+      <c r="G62" s="13" t="n">
+        <v>250</v>
+      </c>
+      <c r="H62" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I62" s="22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="13" t="inlineStr">
+        <is>
+          <t>250 VUs</t>
+        </is>
+      </c>
+      <c r="B63" s="13" t="inlineStr">
+        <is>
+          <t>S06</t>
+        </is>
+      </c>
+      <c r="C63" s="12" t="inlineStr">
+        <is>
+          <t>Doctor Appointments List</t>
+        </is>
+      </c>
+      <c r="D63" s="12" t="inlineStr">
+        <is>
+          <t>Booking Engine</t>
+        </is>
+      </c>
+      <c r="E63" s="12" t="inlineStr">
+        <is>
+          <t>/api/appointments/doctor/:doctorId</t>
+        </is>
+      </c>
+      <c r="F63" s="13" t="n">
+        <v>250</v>
+      </c>
+      <c r="G63" s="13" t="n">
+        <v>250</v>
+      </c>
+      <c r="H63" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I63" s="22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="13" t="inlineStr">
+        <is>
+          <t>250 VUs</t>
+        </is>
+      </c>
+      <c r="B64" s="13" t="inlineStr">
+        <is>
+          <t>S07</t>
+        </is>
+      </c>
+      <c r="C64" s="12" t="inlineStr">
+        <is>
+          <t>Get Appointment Details</t>
+        </is>
+      </c>
+      <c r="D64" s="12" t="inlineStr">
+        <is>
+          <t>Booking Engine</t>
+        </is>
+      </c>
+      <c r="E64" s="12" t="inlineStr">
+        <is>
+          <t>/api/appointments/:id</t>
+        </is>
+      </c>
+      <c r="F64" s="13" t="n">
+        <v>250</v>
+      </c>
+      <c r="G64" s="13" t="n">
+        <v>250</v>
+      </c>
+      <c r="H64" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I64" s="22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="13" t="inlineStr">
+        <is>
+          <t>250 VUs</t>
+        </is>
+      </c>
+      <c r="B65" s="13" t="inlineStr">
+        <is>
+          <t>S08</t>
+        </is>
+      </c>
+      <c r="C65" s="12" t="inlineStr">
+        <is>
+          <t>Queue Registration</t>
+        </is>
+      </c>
+      <c r="D65" s="12" t="inlineStr">
+        <is>
+          <t>Queue Manager</t>
+        </is>
+      </c>
+      <c r="E65" s="12" t="inlineStr">
+        <is>
+          <t>/api/queue</t>
+        </is>
+      </c>
+      <c r="F65" s="13" t="n">
+        <v>250</v>
+      </c>
+      <c r="G65" s="13" t="n">
+        <v>250</v>
+      </c>
+      <c r="H65" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I65" s="22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="13" t="inlineStr">
+        <is>
+          <t>250 VUs</t>
+        </is>
+      </c>
+      <c r="B66" s="13" t="inlineStr">
+        <is>
+          <t>S09</t>
+        </is>
+      </c>
+      <c r="C66" s="12" t="inlineStr">
+        <is>
+          <t>Update Queue Status</t>
+        </is>
+      </c>
+      <c r="D66" s="12" t="inlineStr">
+        <is>
+          <t>Queue Manager</t>
+        </is>
+      </c>
+      <c r="E66" s="12" t="inlineStr">
+        <is>
+          <t>/api/queue/:id/status</t>
+        </is>
+      </c>
+      <c r="F66" s="13" t="n">
+        <v>250</v>
+      </c>
+      <c r="G66" s="13" t="n">
+        <v>250</v>
+      </c>
+      <c r="H66" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I66" s="22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="13" t="inlineStr">
+        <is>
+          <t>250 VUs</t>
+        </is>
+      </c>
+      <c r="B67" s="13" t="inlineStr">
+        <is>
+          <t>S10</t>
+        </is>
+      </c>
+      <c r="C67" s="12" t="inlineStr">
+        <is>
+          <t>Fetch Notifications</t>
+        </is>
+      </c>
+      <c r="D67" s="12" t="inlineStr">
+        <is>
+          <t>Notification Engine</t>
+        </is>
+      </c>
+      <c r="E67" s="12" t="inlineStr">
+        <is>
+          <t>/api/notifications/:userId</t>
+        </is>
+      </c>
+      <c r="F67" s="13" t="n">
+        <v>250</v>
+      </c>
+      <c r="G67" s="13" t="n">
+        <v>250</v>
+      </c>
+      <c r="H67" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I67" s="22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="13" t="inlineStr">
+        <is>
+          <t>250 VUs</t>
+        </is>
+      </c>
+      <c r="B68" s="13" t="inlineStr">
+        <is>
+          <t>S11</t>
+        </is>
+      </c>
+      <c r="C68" s="12" t="inlineStr">
+        <is>
+          <t>Submit Feedback</t>
+        </is>
+      </c>
+      <c r="D68" s="12" t="inlineStr">
+        <is>
+          <t>Feedback System</t>
+        </is>
+      </c>
+      <c r="E68" s="12" t="inlineStr">
+        <is>
+          <t>/api/feedback</t>
+        </is>
+      </c>
+      <c r="F68" s="13" t="n">
+        <v>250</v>
+      </c>
+      <c r="G68" s="13" t="n">
+        <v>250</v>
+      </c>
+      <c r="H68" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I68" s="22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="13" t="inlineStr">
+        <is>
+          <t>250 VUs</t>
+        </is>
+      </c>
+      <c r="B69" s="13" t="inlineStr">
+        <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="C69" s="12" t="inlineStr">
+        <is>
+          <t>Upload Medical Record</t>
+        </is>
+      </c>
+      <c r="D69" s="12" t="inlineStr">
+        <is>
+          <t>Medical Records</t>
+        </is>
+      </c>
+      <c r="E69" s="12" t="inlineStr">
+        <is>
+          <t>/api/medical-records</t>
+        </is>
+      </c>
+      <c r="F69" s="13" t="n">
+        <v>250</v>
+      </c>
+      <c r="G69" s="13" t="n">
+        <v>250</v>
+      </c>
+      <c r="H69" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I69" s="22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="13" t="inlineStr">
+        <is>
+          <t>250 VUs</t>
+        </is>
+      </c>
+      <c r="B70" s="13" t="inlineStr">
+        <is>
+          <t>S13</t>
+        </is>
+      </c>
+      <c r="C70" s="12" t="inlineStr">
+        <is>
+          <t>Patient Dashboard Loading</t>
+        </is>
+      </c>
+      <c r="D70" s="12" t="inlineStr">
+        <is>
+          <t>User Dashboard</t>
+        </is>
+      </c>
+      <c r="E70" s="12" t="inlineStr">
+        <is>
+          <t>/api/dashboard/patient/:patientId</t>
+        </is>
+      </c>
+      <c r="F70" s="13" t="n">
+        <v>250</v>
+      </c>
+      <c r="G70" s="13" t="n">
+        <v>250</v>
+      </c>
+      <c r="H70" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I70" s="22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="13" t="inlineStr">
+        <is>
+          <t>250 VUs</t>
+        </is>
+      </c>
+      <c r="B71" s="13" t="inlineStr">
+        <is>
+          <t>S14</t>
+        </is>
+      </c>
+      <c r="C71" s="12" t="inlineStr">
+        <is>
+          <t>Doctor Dashboard Loading</t>
+        </is>
+      </c>
+      <c r="D71" s="12" t="inlineStr">
+        <is>
+          <t>User Dashboard</t>
+        </is>
+      </c>
+      <c r="E71" s="12" t="inlineStr">
+        <is>
+          <t>/api/dashboard/doctor/:doctorId</t>
+        </is>
+      </c>
+      <c r="F71" s="13" t="n">
+        <v>250</v>
+      </c>
+      <c r="G71" s="13" t="n">
+        <v>250</v>
+      </c>
+      <c r="H71" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I71" s="22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="13" t="inlineStr">
+        <is>
+          <t>500 VUs</t>
+        </is>
+      </c>
+      <c r="B72" s="13" t="inlineStr">
+        <is>
+          <t>S01</t>
+        </is>
+      </c>
+      <c r="C72" s="12" t="inlineStr">
+        <is>
+          <t>User Login</t>
+        </is>
+      </c>
+      <c r="D72" s="12" t="inlineStr">
+        <is>
+          <t>Authentication</t>
+        </is>
+      </c>
+      <c r="E72" s="12" t="inlineStr">
+        <is>
+          <t>/api/auth/login</t>
+        </is>
+      </c>
+      <c r="F72" s="13" t="n">
+        <v>500</v>
+      </c>
+      <c r="G72" s="13" t="n">
+        <v>500</v>
+      </c>
+      <c r="H72" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I72" s="22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="13" t="inlineStr">
+        <is>
+          <t>500 VUs</t>
+        </is>
+      </c>
+      <c r="B73" s="13" t="inlineStr">
+        <is>
+          <t>S02</t>
+        </is>
+      </c>
+      <c r="C73" s="12" t="inlineStr">
+        <is>
+          <t>User Registration</t>
+        </is>
+      </c>
+      <c r="D73" s="12" t="inlineStr">
+        <is>
+          <t>Authentication</t>
+        </is>
+      </c>
+      <c r="E73" s="12" t="inlineStr">
+        <is>
+          <t>/api/auth/register</t>
+        </is>
+      </c>
+      <c r="F73" s="13" t="n">
+        <v>500</v>
+      </c>
+      <c r="G73" s="13" t="n">
+        <v>500</v>
+      </c>
+      <c r="H73" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I73" s="22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="13" t="inlineStr">
+        <is>
+          <t>500 VUs</t>
+        </is>
+      </c>
+      <c r="B74" s="13" t="inlineStr">
+        <is>
+          <t>S03</t>
+        </is>
+      </c>
+      <c r="C74" s="12" t="inlineStr">
+        <is>
+          <t>Update Doctor Profile</t>
+        </is>
+      </c>
+      <c r="D74" s="12" t="inlineStr">
+        <is>
+          <t>Doctor Portal</t>
+        </is>
+      </c>
+      <c r="E74" s="12" t="inlineStr">
+        <is>
+          <t>/api/doctors/:id/profile</t>
+        </is>
+      </c>
+      <c r="F74" s="13" t="n">
+        <v>500</v>
+      </c>
+      <c r="G74" s="13" t="n">
+        <v>500</v>
+      </c>
+      <c r="H74" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I74" s="22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="13" t="inlineStr">
+        <is>
+          <t>500 VUs</t>
+        </is>
+      </c>
+      <c r="B75" s="13" t="inlineStr">
+        <is>
+          <t>S04</t>
+        </is>
+      </c>
+      <c r="C75" s="12" t="inlineStr">
+        <is>
+          <t>Book Appointment</t>
+        </is>
+      </c>
+      <c r="D75" s="12" t="inlineStr">
+        <is>
+          <t>Booking Engine</t>
+        </is>
+      </c>
+      <c r="E75" s="12" t="inlineStr">
+        <is>
+          <t>/api/appointments</t>
+        </is>
+      </c>
+      <c r="F75" s="13" t="n">
+        <v>500</v>
+      </c>
+      <c r="G75" s="13" t="n">
+        <v>500</v>
+      </c>
+      <c r="H75" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I75" s="22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="13" t="inlineStr">
+        <is>
+          <t>500 VUs</t>
+        </is>
+      </c>
+      <c r="B76" s="13" t="inlineStr">
+        <is>
+          <t>S05</t>
+        </is>
+      </c>
+      <c r="C76" s="12" t="inlineStr">
+        <is>
+          <t>Patient Appointments List</t>
+        </is>
+      </c>
+      <c r="D76" s="12" t="inlineStr">
+        <is>
+          <t>Booking Engine</t>
+        </is>
+      </c>
+      <c r="E76" s="12" t="inlineStr">
+        <is>
+          <t>/api/appointments/patient/:patientId</t>
+        </is>
+      </c>
+      <c r="F76" s="13" t="n">
+        <v>500</v>
+      </c>
+      <c r="G76" s="13" t="n">
+        <v>500</v>
+      </c>
+      <c r="H76" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I76" s="22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="13" t="inlineStr">
+        <is>
+          <t>500 VUs</t>
+        </is>
+      </c>
+      <c r="B77" s="13" t="inlineStr">
+        <is>
+          <t>S06</t>
+        </is>
+      </c>
+      <c r="C77" s="12" t="inlineStr">
+        <is>
+          <t>Doctor Appointments List</t>
+        </is>
+      </c>
+      <c r="D77" s="12" t="inlineStr">
+        <is>
+          <t>Booking Engine</t>
+        </is>
+      </c>
+      <c r="E77" s="12" t="inlineStr">
+        <is>
+          <t>/api/appointments/doctor/:doctorId</t>
+        </is>
+      </c>
+      <c r="F77" s="13" t="n">
+        <v>500</v>
+      </c>
+      <c r="G77" s="13" t="n">
+        <v>500</v>
+      </c>
+      <c r="H77" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I77" s="22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="13" t="inlineStr">
+        <is>
+          <t>500 VUs</t>
+        </is>
+      </c>
+      <c r="B78" s="13" t="inlineStr">
+        <is>
+          <t>S07</t>
+        </is>
+      </c>
+      <c r="C78" s="12" t="inlineStr">
+        <is>
+          <t>Get Appointment Details</t>
+        </is>
+      </c>
+      <c r="D78" s="12" t="inlineStr">
+        <is>
+          <t>Booking Engine</t>
+        </is>
+      </c>
+      <c r="E78" s="12" t="inlineStr">
+        <is>
+          <t>/api/appointments/:id</t>
+        </is>
+      </c>
+      <c r="F78" s="13" t="n">
+        <v>500</v>
+      </c>
+      <c r="G78" s="13" t="n">
+        <v>500</v>
+      </c>
+      <c r="H78" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I78" s="22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="13" t="inlineStr">
+        <is>
+          <t>500 VUs</t>
+        </is>
+      </c>
+      <c r="B79" s="13" t="inlineStr">
+        <is>
+          <t>S08</t>
+        </is>
+      </c>
+      <c r="C79" s="12" t="inlineStr">
+        <is>
+          <t>Queue Registration</t>
+        </is>
+      </c>
+      <c r="D79" s="12" t="inlineStr">
+        <is>
+          <t>Queue Manager</t>
+        </is>
+      </c>
+      <c r="E79" s="12" t="inlineStr">
+        <is>
+          <t>/api/queue</t>
+        </is>
+      </c>
+      <c r="F79" s="13" t="n">
+        <v>500</v>
+      </c>
+      <c r="G79" s="13" t="n">
+        <v>500</v>
+      </c>
+      <c r="H79" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I79" s="22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="13" t="inlineStr">
+        <is>
+          <t>500 VUs</t>
+        </is>
+      </c>
+      <c r="B80" s="13" t="inlineStr">
+        <is>
+          <t>S09</t>
+        </is>
+      </c>
+      <c r="C80" s="12" t="inlineStr">
+        <is>
+          <t>Update Queue Status</t>
+        </is>
+      </c>
+      <c r="D80" s="12" t="inlineStr">
+        <is>
+          <t>Queue Manager</t>
+        </is>
+      </c>
+      <c r="E80" s="12" t="inlineStr">
+        <is>
+          <t>/api/queue/:id/status</t>
+        </is>
+      </c>
+      <c r="F80" s="13" t="n">
+        <v>500</v>
+      </c>
+      <c r="G80" s="13" t="n">
+        <v>500</v>
+      </c>
+      <c r="H80" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I80" s="22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="13" t="inlineStr">
+        <is>
+          <t>500 VUs</t>
+        </is>
+      </c>
+      <c r="B81" s="13" t="inlineStr">
+        <is>
+          <t>S10</t>
+        </is>
+      </c>
+      <c r="C81" s="12" t="inlineStr">
+        <is>
+          <t>Fetch Notifications</t>
+        </is>
+      </c>
+      <c r="D81" s="12" t="inlineStr">
+        <is>
+          <t>Notification Engine</t>
+        </is>
+      </c>
+      <c r="E81" s="12" t="inlineStr">
+        <is>
+          <t>/api/notifications/:userId</t>
+        </is>
+      </c>
+      <c r="F81" s="13" t="n">
+        <v>500</v>
+      </c>
+      <c r="G81" s="13" t="n">
+        <v>500</v>
+      </c>
+      <c r="H81" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I81" s="22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="13" t="inlineStr">
+        <is>
+          <t>500 VUs</t>
+        </is>
+      </c>
+      <c r="B82" s="13" t="inlineStr">
+        <is>
+          <t>S11</t>
+        </is>
+      </c>
+      <c r="C82" s="12" t="inlineStr">
+        <is>
+          <t>Submit Feedback</t>
+        </is>
+      </c>
+      <c r="D82" s="12" t="inlineStr">
+        <is>
+          <t>Feedback System</t>
+        </is>
+      </c>
+      <c r="E82" s="12" t="inlineStr">
+        <is>
+          <t>/api/feedback</t>
+        </is>
+      </c>
+      <c r="F82" s="13" t="n">
+        <v>500</v>
+      </c>
+      <c r="G82" s="13" t="n">
+        <v>500</v>
+      </c>
+      <c r="H82" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I82" s="22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="13" t="inlineStr">
+        <is>
+          <t>500 VUs</t>
+        </is>
+      </c>
+      <c r="B83" s="13" t="inlineStr">
+        <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="C83" s="12" t="inlineStr">
+        <is>
+          <t>Upload Medical Record</t>
+        </is>
+      </c>
+      <c r="D83" s="12" t="inlineStr">
+        <is>
+          <t>Medical Records</t>
+        </is>
+      </c>
+      <c r="E83" s="12" t="inlineStr">
+        <is>
+          <t>/api/medical-records</t>
+        </is>
+      </c>
+      <c r="F83" s="13" t="n">
+        <v>500</v>
+      </c>
+      <c r="G83" s="13" t="n">
+        <v>500</v>
+      </c>
+      <c r="H83" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I83" s="22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="13" t="inlineStr">
+        <is>
+          <t>500 VUs</t>
+        </is>
+      </c>
+      <c r="B84" s="13" t="inlineStr">
+        <is>
+          <t>S13</t>
+        </is>
+      </c>
+      <c r="C84" s="12" t="inlineStr">
+        <is>
+          <t>Patient Dashboard Loading</t>
+        </is>
+      </c>
+      <c r="D84" s="12" t="inlineStr">
+        <is>
+          <t>User Dashboard</t>
+        </is>
+      </c>
+      <c r="E84" s="12" t="inlineStr">
+        <is>
+          <t>/api/dashboard/patient/:patientId</t>
+        </is>
+      </c>
+      <c r="F84" s="13" t="n">
+        <v>500</v>
+      </c>
+      <c r="G84" s="13" t="n">
+        <v>500</v>
+      </c>
+      <c r="H84" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I84" s="22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="13" t="inlineStr">
+        <is>
+          <t>500 VUs</t>
+        </is>
+      </c>
+      <c r="B85" s="13" t="inlineStr">
+        <is>
+          <t>S14</t>
+        </is>
+      </c>
+      <c r="C85" s="12" t="inlineStr">
+        <is>
+          <t>Doctor Dashboard Loading</t>
+        </is>
+      </c>
+      <c r="D85" s="12" t="inlineStr">
+        <is>
+          <t>User Dashboard</t>
+        </is>
+      </c>
+      <c r="E85" s="12" t="inlineStr">
+        <is>
+          <t>/api/dashboard/doctor/:doctorId</t>
+        </is>
+      </c>
+      <c r="F85" s="13" t="n">
+        <v>500</v>
+      </c>
+      <c r="G85" s="13" t="n">
+        <v>500</v>
+      </c>
+      <c r="H85" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I85" s="22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="13" t="inlineStr">
+        <is>
+          <t>1000 VUs</t>
+        </is>
+      </c>
+      <c r="B86" s="13" t="inlineStr">
+        <is>
+          <t>S01</t>
+        </is>
+      </c>
+      <c r="C86" s="12" t="inlineStr">
+        <is>
+          <t>User Login</t>
+        </is>
+      </c>
+      <c r="D86" s="12" t="inlineStr">
+        <is>
+          <t>Authentication</t>
+        </is>
+      </c>
+      <c r="E86" s="12" t="inlineStr">
+        <is>
+          <t>/api/auth/login</t>
+        </is>
+      </c>
+      <c r="F86" s="13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="G86" s="13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H86" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I86" s="22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="13" t="inlineStr">
+        <is>
+          <t>1000 VUs</t>
+        </is>
+      </c>
+      <c r="B87" s="13" t="inlineStr">
+        <is>
+          <t>S02</t>
+        </is>
+      </c>
+      <c r="C87" s="12" t="inlineStr">
+        <is>
+          <t>User Registration</t>
+        </is>
+      </c>
+      <c r="D87" s="12" t="inlineStr">
+        <is>
+          <t>Authentication</t>
+        </is>
+      </c>
+      <c r="E87" s="12" t="inlineStr">
+        <is>
+          <t>/api/auth/register</t>
+        </is>
+      </c>
+      <c r="F87" s="13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="G87" s="13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H87" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I87" s="22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="13" t="inlineStr">
+        <is>
+          <t>1000 VUs</t>
+        </is>
+      </c>
+      <c r="B88" s="13" t="inlineStr">
+        <is>
+          <t>S03</t>
+        </is>
+      </c>
+      <c r="C88" s="12" t="inlineStr">
+        <is>
+          <t>Update Doctor Profile</t>
+        </is>
+      </c>
+      <c r="D88" s="12" t="inlineStr">
+        <is>
+          <t>Doctor Portal</t>
+        </is>
+      </c>
+      <c r="E88" s="12" t="inlineStr">
+        <is>
+          <t>/api/doctors/:id/profile</t>
+        </is>
+      </c>
+      <c r="F88" s="13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="G88" s="13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H88" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I88" s="22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="13" t="inlineStr">
+        <is>
+          <t>1000 VUs</t>
+        </is>
+      </c>
+      <c r="B89" s="13" t="inlineStr">
+        <is>
+          <t>S04</t>
+        </is>
+      </c>
+      <c r="C89" s="12" t="inlineStr">
+        <is>
+          <t>Book Appointment</t>
+        </is>
+      </c>
+      <c r="D89" s="12" t="inlineStr">
+        <is>
+          <t>Booking Engine</t>
+        </is>
+      </c>
+      <c r="E89" s="12" t="inlineStr">
+        <is>
+          <t>/api/appointments</t>
+        </is>
+      </c>
+      <c r="F89" s="13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="G89" s="13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H89" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I89" s="22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="13" t="inlineStr">
+        <is>
+          <t>1000 VUs</t>
+        </is>
+      </c>
+      <c r="B90" s="13" t="inlineStr">
+        <is>
+          <t>S05</t>
+        </is>
+      </c>
+      <c r="C90" s="12" t="inlineStr">
+        <is>
+          <t>Patient Appointments List</t>
+        </is>
+      </c>
+      <c r="D90" s="12" t="inlineStr">
+        <is>
+          <t>Booking Engine</t>
+        </is>
+      </c>
+      <c r="E90" s="12" t="inlineStr">
+        <is>
+          <t>/api/appointments/patient/:patientId</t>
+        </is>
+      </c>
+      <c r="F90" s="13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="G90" s="13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H90" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I90" s="22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="13" t="inlineStr">
+        <is>
+          <t>1000 VUs</t>
+        </is>
+      </c>
+      <c r="B91" s="13" t="inlineStr">
+        <is>
+          <t>S06</t>
+        </is>
+      </c>
+      <c r="C91" s="12" t="inlineStr">
+        <is>
+          <t>Doctor Appointments List</t>
+        </is>
+      </c>
+      <c r="D91" s="12" t="inlineStr">
+        <is>
+          <t>Booking Engine</t>
+        </is>
+      </c>
+      <c r="E91" s="12" t="inlineStr">
+        <is>
+          <t>/api/appointments/doctor/:doctorId</t>
+        </is>
+      </c>
+      <c r="F91" s="13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="G91" s="13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H91" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I91" s="22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="13" t="inlineStr">
+        <is>
+          <t>1000 VUs</t>
+        </is>
+      </c>
+      <c r="B92" s="13" t="inlineStr">
+        <is>
+          <t>S07</t>
+        </is>
+      </c>
+      <c r="C92" s="12" t="inlineStr">
+        <is>
+          <t>Get Appointment Details</t>
+        </is>
+      </c>
+      <c r="D92" s="12" t="inlineStr">
+        <is>
+          <t>Booking Engine</t>
+        </is>
+      </c>
+      <c r="E92" s="12" t="inlineStr">
+        <is>
+          <t>/api/appointments/:id</t>
+        </is>
+      </c>
+      <c r="F92" s="13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="G92" s="13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H92" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I92" s="22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="13" t="inlineStr">
+        <is>
+          <t>1000 VUs</t>
+        </is>
+      </c>
+      <c r="B93" s="13" t="inlineStr">
+        <is>
+          <t>S08</t>
+        </is>
+      </c>
+      <c r="C93" s="12" t="inlineStr">
+        <is>
+          <t>Queue Registration</t>
+        </is>
+      </c>
+      <c r="D93" s="12" t="inlineStr">
+        <is>
+          <t>Queue Manager</t>
+        </is>
+      </c>
+      <c r="E93" s="12" t="inlineStr">
+        <is>
+          <t>/api/queue</t>
+        </is>
+      </c>
+      <c r="F93" s="13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="G93" s="13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H93" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I93" s="22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="13" t="inlineStr">
+        <is>
+          <t>1000 VUs</t>
+        </is>
+      </c>
+      <c r="B94" s="13" t="inlineStr">
+        <is>
+          <t>S09</t>
+        </is>
+      </c>
+      <c r="C94" s="12" t="inlineStr">
+        <is>
+          <t>Update Queue Status</t>
+        </is>
+      </c>
+      <c r="D94" s="12" t="inlineStr">
+        <is>
+          <t>Queue Manager</t>
+        </is>
+      </c>
+      <c r="E94" s="12" t="inlineStr">
+        <is>
+          <t>/api/queue/:id/status</t>
+        </is>
+      </c>
+      <c r="F94" s="13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="G94" s="13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H94" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I94" s="22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="13" t="inlineStr">
+        <is>
+          <t>1000 VUs</t>
+        </is>
+      </c>
+      <c r="B95" s="13" t="inlineStr">
+        <is>
+          <t>S10</t>
+        </is>
+      </c>
+      <c r="C95" s="12" t="inlineStr">
+        <is>
+          <t>Fetch Notifications</t>
+        </is>
+      </c>
+      <c r="D95" s="12" t="inlineStr">
+        <is>
+          <t>Notification Engine</t>
+        </is>
+      </c>
+      <c r="E95" s="12" t="inlineStr">
+        <is>
+          <t>/api/notifications/:userId</t>
+        </is>
+      </c>
+      <c r="F95" s="13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="G95" s="13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H95" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I95" s="22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="13" t="inlineStr">
+        <is>
+          <t>1000 VUs</t>
+        </is>
+      </c>
+      <c r="B96" s="13" t="inlineStr">
+        <is>
+          <t>S11</t>
+        </is>
+      </c>
+      <c r="C96" s="12" t="inlineStr">
+        <is>
+          <t>Submit Feedback</t>
+        </is>
+      </c>
+      <c r="D96" s="12" t="inlineStr">
+        <is>
+          <t>Feedback System</t>
+        </is>
+      </c>
+      <c r="E96" s="12" t="inlineStr">
+        <is>
+          <t>/api/feedback</t>
+        </is>
+      </c>
+      <c r="F96" s="13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="G96" s="13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H96" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I96" s="22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="13" t="inlineStr">
+        <is>
+          <t>1000 VUs</t>
+        </is>
+      </c>
+      <c r="B97" s="13" t="inlineStr">
+        <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="C97" s="12" t="inlineStr">
+        <is>
+          <t>Upload Medical Record</t>
+        </is>
+      </c>
+      <c r="D97" s="12" t="inlineStr">
+        <is>
+          <t>Medical Records</t>
+        </is>
+      </c>
+      <c r="E97" s="12" t="inlineStr">
+        <is>
+          <t>/api/medical-records</t>
+        </is>
+      </c>
+      <c r="F97" s="13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="G97" s="13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H97" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I97" s="22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="13" t="inlineStr">
+        <is>
+          <t>1000 VUs</t>
+        </is>
+      </c>
+      <c r="B98" s="13" t="inlineStr">
+        <is>
+          <t>S13</t>
+        </is>
+      </c>
+      <c r="C98" s="12" t="inlineStr">
+        <is>
+          <t>Patient Dashboard Loading</t>
+        </is>
+      </c>
+      <c r="D98" s="12" t="inlineStr">
+        <is>
+          <t>User Dashboard</t>
+        </is>
+      </c>
+      <c r="E98" s="12" t="inlineStr">
+        <is>
+          <t>/api/dashboard/patient/:patientId</t>
+        </is>
+      </c>
+      <c r="F98" s="13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="G98" s="13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H98" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I98" s="22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="13" t="inlineStr">
+        <is>
+          <t>1000 VUs</t>
+        </is>
+      </c>
+      <c r="B99" s="13" t="inlineStr">
+        <is>
+          <t>S14</t>
+        </is>
+      </c>
+      <c r="C99" s="12" t="inlineStr">
+        <is>
+          <t>Doctor Dashboard Loading</t>
+        </is>
+      </c>
+      <c r="D99" s="12" t="inlineStr">
+        <is>
+          <t>User Dashboard</t>
+        </is>
+      </c>
+      <c r="E99" s="12" t="inlineStr">
+        <is>
+          <t>/api/dashboard/doctor/:doctorId</t>
+        </is>
+      </c>
+      <c r="F99" s="13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="G99" s="13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H99" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I99" s="22" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1233,13 +5106,3782 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:H99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="21" customWidth="1" min="7" max="7"/>
+    <col width="23" customWidth="1" min="8" max="8"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="21" t="inlineStr">
-        <is>
-          <t>Database read/write load and cloud resources usage metrics.</t>
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>VU Level</t>
+        </is>
+      </c>
+      <c r="B1" s="5" t="inlineStr">
+        <is>
+          <t>Scenario ID</t>
+        </is>
+      </c>
+      <c r="C1" s="21" t="inlineStr">
+        <is>
+          <t>Module Scenario</t>
+        </is>
+      </c>
+      <c r="D1" s="5" t="inlineStr">
+        <is>
+          <t>RAM Memory Usage (MB)</t>
+        </is>
+      </c>
+      <c r="E1" s="5" t="inlineStr">
+        <is>
+          <t>CPU Utilization (%)</t>
+        </is>
+      </c>
+      <c r="F1" s="5" t="inlineStr">
+        <is>
+          <t>Firebase Read Ops</t>
+        </is>
+      </c>
+      <c r="G1" s="5" t="inlineStr">
+        <is>
+          <t>Firebase Write Ops</t>
+        </is>
+      </c>
+      <c r="H1" s="5" t="inlineStr">
+        <is>
+          <t>Network Latency (ms)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="13" t="inlineStr">
+        <is>
+          <t>10 VUs</t>
+        </is>
+      </c>
+      <c r="B2" s="13" t="inlineStr">
+        <is>
+          <t>S01</t>
+        </is>
+      </c>
+      <c r="C2" s="12" t="inlineStr">
+        <is>
+          <t>User Login</t>
+        </is>
+      </c>
+      <c r="D2" s="13" t="inlineStr">
+        <is>
+          <t>154 MB</t>
+        </is>
+      </c>
+      <c r="E2" s="13" t="inlineStr">
+        <is>
+          <t>5.8%</t>
+        </is>
+      </c>
+      <c r="F2" s="13" t="n">
+        <v>20</v>
+      </c>
+      <c r="G2" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" s="13" t="inlineStr">
+        <is>
+          <t>10 ms</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>10 VUs</t>
+        </is>
+      </c>
+      <c r="B3" s="13" t="inlineStr">
+        <is>
+          <t>S02</t>
+        </is>
+      </c>
+      <c r="C3" s="12" t="inlineStr">
+        <is>
+          <t>User Registration</t>
+        </is>
+      </c>
+      <c r="D3" s="13" t="inlineStr">
+        <is>
+          <t>154 MB</t>
+        </is>
+      </c>
+      <c r="E3" s="13" t="inlineStr">
+        <is>
+          <t>5.8%</t>
+        </is>
+      </c>
+      <c r="F3" s="13" t="n">
+        <v>20</v>
+      </c>
+      <c r="G3" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" s="13" t="inlineStr">
+        <is>
+          <t>10 ms</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="13" t="inlineStr">
+        <is>
+          <t>10 VUs</t>
+        </is>
+      </c>
+      <c r="B4" s="13" t="inlineStr">
+        <is>
+          <t>S03</t>
+        </is>
+      </c>
+      <c r="C4" s="12" t="inlineStr">
+        <is>
+          <t>Update Doctor Profile</t>
+        </is>
+      </c>
+      <c r="D4" s="13" t="inlineStr">
+        <is>
+          <t>154 MB</t>
+        </is>
+      </c>
+      <c r="E4" s="13" t="inlineStr">
+        <is>
+          <t>5.8%</t>
+        </is>
+      </c>
+      <c r="F4" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" s="13" t="n">
+        <v>10</v>
+      </c>
+      <c r="H4" s="13" t="inlineStr">
+        <is>
+          <t>10 ms</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="13" t="inlineStr">
+        <is>
+          <t>10 VUs</t>
+        </is>
+      </c>
+      <c r="B5" s="13" t="inlineStr">
+        <is>
+          <t>S04</t>
+        </is>
+      </c>
+      <c r="C5" s="12" t="inlineStr">
+        <is>
+          <t>Book Appointment</t>
+        </is>
+      </c>
+      <c r="D5" s="13" t="inlineStr">
+        <is>
+          <t>154 MB</t>
+        </is>
+      </c>
+      <c r="E5" s="13" t="inlineStr">
+        <is>
+          <t>5.8%</t>
+        </is>
+      </c>
+      <c r="F5" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" s="13" t="n">
+        <v>10</v>
+      </c>
+      <c r="H5" s="13" t="inlineStr">
+        <is>
+          <t>10 ms</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="13" t="inlineStr">
+        <is>
+          <t>10 VUs</t>
+        </is>
+      </c>
+      <c r="B6" s="13" t="inlineStr">
+        <is>
+          <t>S05</t>
+        </is>
+      </c>
+      <c r="C6" s="12" t="inlineStr">
+        <is>
+          <t>Patient Appointments List</t>
+        </is>
+      </c>
+      <c r="D6" s="13" t="inlineStr">
+        <is>
+          <t>154 MB</t>
+        </is>
+      </c>
+      <c r="E6" s="13" t="inlineStr">
+        <is>
+          <t>5.8%</t>
+        </is>
+      </c>
+      <c r="F6" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" s="13" t="inlineStr">
+        <is>
+          <t>10 ms</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="13" t="inlineStr">
+        <is>
+          <t>10 VUs</t>
+        </is>
+      </c>
+      <c r="B7" s="13" t="inlineStr">
+        <is>
+          <t>S06</t>
+        </is>
+      </c>
+      <c r="C7" s="12" t="inlineStr">
+        <is>
+          <t>Doctor Appointments List</t>
+        </is>
+      </c>
+      <c r="D7" s="13" t="inlineStr">
+        <is>
+          <t>154 MB</t>
+        </is>
+      </c>
+      <c r="E7" s="13" t="inlineStr">
+        <is>
+          <t>5.8%</t>
+        </is>
+      </c>
+      <c r="F7" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" s="13" t="inlineStr">
+        <is>
+          <t>10 ms</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="13" t="inlineStr">
+        <is>
+          <t>10 VUs</t>
+        </is>
+      </c>
+      <c r="B8" s="13" t="inlineStr">
+        <is>
+          <t>S07</t>
+        </is>
+      </c>
+      <c r="C8" s="12" t="inlineStr">
+        <is>
+          <t>Get Appointment Details</t>
+        </is>
+      </c>
+      <c r="D8" s="13" t="inlineStr">
+        <is>
+          <t>154 MB</t>
+        </is>
+      </c>
+      <c r="E8" s="13" t="inlineStr">
+        <is>
+          <t>5.8%</t>
+        </is>
+      </c>
+      <c r="F8" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" s="13" t="inlineStr">
+        <is>
+          <t>10 ms</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="13" t="inlineStr">
+        <is>
+          <t>10 VUs</t>
+        </is>
+      </c>
+      <c r="B9" s="13" t="inlineStr">
+        <is>
+          <t>S08</t>
+        </is>
+      </c>
+      <c r="C9" s="12" t="inlineStr">
+        <is>
+          <t>Queue Registration</t>
+        </is>
+      </c>
+      <c r="D9" s="13" t="inlineStr">
+        <is>
+          <t>154 MB</t>
+        </is>
+      </c>
+      <c r="E9" s="13" t="inlineStr">
+        <is>
+          <t>5.8%</t>
+        </is>
+      </c>
+      <c r="F9" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" s="13" t="n">
+        <v>10</v>
+      </c>
+      <c r="H9" s="13" t="inlineStr">
+        <is>
+          <t>10 ms</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="13" t="inlineStr">
+        <is>
+          <t>10 VUs</t>
+        </is>
+      </c>
+      <c r="B10" s="13" t="inlineStr">
+        <is>
+          <t>S09</t>
+        </is>
+      </c>
+      <c r="C10" s="12" t="inlineStr">
+        <is>
+          <t>Update Queue Status</t>
+        </is>
+      </c>
+      <c r="D10" s="13" t="inlineStr">
+        <is>
+          <t>154 MB</t>
+        </is>
+      </c>
+      <c r="E10" s="13" t="inlineStr">
+        <is>
+          <t>5.8%</t>
+        </is>
+      </c>
+      <c r="F10" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" s="13" t="n">
+        <v>10</v>
+      </c>
+      <c r="H10" s="13" t="inlineStr">
+        <is>
+          <t>10 ms</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="13" t="inlineStr">
+        <is>
+          <t>10 VUs</t>
+        </is>
+      </c>
+      <c r="B11" s="13" t="inlineStr">
+        <is>
+          <t>S10</t>
+        </is>
+      </c>
+      <c r="C11" s="12" t="inlineStr">
+        <is>
+          <t>Fetch Notifications</t>
+        </is>
+      </c>
+      <c r="D11" s="13" t="inlineStr">
+        <is>
+          <t>154 MB</t>
+        </is>
+      </c>
+      <c r="E11" s="13" t="inlineStr">
+        <is>
+          <t>5.8%</t>
+        </is>
+      </c>
+      <c r="F11" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" s="13" t="n">
+        <v>10</v>
+      </c>
+      <c r="H11" s="13" t="inlineStr">
+        <is>
+          <t>10 ms</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="13" t="inlineStr">
+        <is>
+          <t>10 VUs</t>
+        </is>
+      </c>
+      <c r="B12" s="13" t="inlineStr">
+        <is>
+          <t>S11</t>
+        </is>
+      </c>
+      <c r="C12" s="12" t="inlineStr">
+        <is>
+          <t>Submit Feedback</t>
+        </is>
+      </c>
+      <c r="D12" s="13" t="inlineStr">
+        <is>
+          <t>154 MB</t>
+        </is>
+      </c>
+      <c r="E12" s="13" t="inlineStr">
+        <is>
+          <t>5.8%</t>
+        </is>
+      </c>
+      <c r="F12" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" s="13" t="n">
+        <v>10</v>
+      </c>
+      <c r="H12" s="13" t="inlineStr">
+        <is>
+          <t>10 ms</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="13" t="inlineStr">
+        <is>
+          <t>10 VUs</t>
+        </is>
+      </c>
+      <c r="B13" s="13" t="inlineStr">
+        <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="C13" s="12" t="inlineStr">
+        <is>
+          <t>Upload Medical Record</t>
+        </is>
+      </c>
+      <c r="D13" s="13" t="inlineStr">
+        <is>
+          <t>164 MB</t>
+        </is>
+      </c>
+      <c r="E13" s="13" t="inlineStr">
+        <is>
+          <t>5.8%</t>
+        </is>
+      </c>
+      <c r="F13" s="13" t="n">
+        <v>20</v>
+      </c>
+      <c r="G13" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" s="13" t="inlineStr">
+        <is>
+          <t>10 ms</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="13" t="inlineStr">
+        <is>
+          <t>10 VUs</t>
+        </is>
+      </c>
+      <c r="B14" s="13" t="inlineStr">
+        <is>
+          <t>S13</t>
+        </is>
+      </c>
+      <c r="C14" s="12" t="inlineStr">
+        <is>
+          <t>Patient Dashboard Loading</t>
+        </is>
+      </c>
+      <c r="D14" s="13" t="inlineStr">
+        <is>
+          <t>154 MB</t>
+        </is>
+      </c>
+      <c r="E14" s="13" t="inlineStr">
+        <is>
+          <t>7.3%</t>
+        </is>
+      </c>
+      <c r="F14" s="13" t="n">
+        <v>20</v>
+      </c>
+      <c r="G14" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" s="13" t="inlineStr">
+        <is>
+          <t>10 ms</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="13" t="inlineStr">
+        <is>
+          <t>10 VUs</t>
+        </is>
+      </c>
+      <c r="B15" s="13" t="inlineStr">
+        <is>
+          <t>S14</t>
+        </is>
+      </c>
+      <c r="C15" s="12" t="inlineStr">
+        <is>
+          <t>Doctor Dashboard Loading</t>
+        </is>
+      </c>
+      <c r="D15" s="13" t="inlineStr">
+        <is>
+          <t>154 MB</t>
+        </is>
+      </c>
+      <c r="E15" s="13" t="inlineStr">
+        <is>
+          <t>5.8%</t>
+        </is>
+      </c>
+      <c r="F15" s="13" t="n">
+        <v>20</v>
+      </c>
+      <c r="G15" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" s="13" t="inlineStr">
+        <is>
+          <t>10 ms</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="13" t="inlineStr">
+        <is>
+          <t>25 VUs</t>
+        </is>
+      </c>
+      <c r="B16" s="13" t="inlineStr">
+        <is>
+          <t>S01</t>
+        </is>
+      </c>
+      <c r="C16" s="12" t="inlineStr">
+        <is>
+          <t>User Login</t>
+        </is>
+      </c>
+      <c r="D16" s="13" t="inlineStr">
+        <is>
+          <t>160 MB</t>
+        </is>
+      </c>
+      <c r="E16" s="13" t="inlineStr">
+        <is>
+          <t>7.0%</t>
+        </is>
+      </c>
+      <c r="F16" s="13" t="n">
+        <v>50</v>
+      </c>
+      <c r="G16" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" s="13" t="inlineStr">
+        <is>
+          <t>10 ms</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="13" t="inlineStr">
+        <is>
+          <t>25 VUs</t>
+        </is>
+      </c>
+      <c r="B17" s="13" t="inlineStr">
+        <is>
+          <t>S02</t>
+        </is>
+      </c>
+      <c r="C17" s="12" t="inlineStr">
+        <is>
+          <t>User Registration</t>
+        </is>
+      </c>
+      <c r="D17" s="13" t="inlineStr">
+        <is>
+          <t>160 MB</t>
+        </is>
+      </c>
+      <c r="E17" s="13" t="inlineStr">
+        <is>
+          <t>7.0%</t>
+        </is>
+      </c>
+      <c r="F17" s="13" t="n">
+        <v>50</v>
+      </c>
+      <c r="G17" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" s="13" t="inlineStr">
+        <is>
+          <t>10 ms</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="13" t="inlineStr">
+        <is>
+          <t>25 VUs</t>
+        </is>
+      </c>
+      <c r="B18" s="13" t="inlineStr">
+        <is>
+          <t>S03</t>
+        </is>
+      </c>
+      <c r="C18" s="12" t="inlineStr">
+        <is>
+          <t>Update Doctor Profile</t>
+        </is>
+      </c>
+      <c r="D18" s="13" t="inlineStr">
+        <is>
+          <t>160 MB</t>
+        </is>
+      </c>
+      <c r="E18" s="13" t="inlineStr">
+        <is>
+          <t>7.0%</t>
+        </is>
+      </c>
+      <c r="F18" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" s="13" t="n">
+        <v>25</v>
+      </c>
+      <c r="H18" s="13" t="inlineStr">
+        <is>
+          <t>10 ms</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="13" t="inlineStr">
+        <is>
+          <t>25 VUs</t>
+        </is>
+      </c>
+      <c r="B19" s="13" t="inlineStr">
+        <is>
+          <t>S04</t>
+        </is>
+      </c>
+      <c r="C19" s="12" t="inlineStr">
+        <is>
+          <t>Book Appointment</t>
+        </is>
+      </c>
+      <c r="D19" s="13" t="inlineStr">
+        <is>
+          <t>160 MB</t>
+        </is>
+      </c>
+      <c r="E19" s="13" t="inlineStr">
+        <is>
+          <t>7.0%</t>
+        </is>
+      </c>
+      <c r="F19" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" s="13" t="n">
+        <v>25</v>
+      </c>
+      <c r="H19" s="13" t="inlineStr">
+        <is>
+          <t>10 ms</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="13" t="inlineStr">
+        <is>
+          <t>25 VUs</t>
+        </is>
+      </c>
+      <c r="B20" s="13" t="inlineStr">
+        <is>
+          <t>S05</t>
+        </is>
+      </c>
+      <c r="C20" s="12" t="inlineStr">
+        <is>
+          <t>Patient Appointments List</t>
+        </is>
+      </c>
+      <c r="D20" s="13" t="inlineStr">
+        <is>
+          <t>160 MB</t>
+        </is>
+      </c>
+      <c r="E20" s="13" t="inlineStr">
+        <is>
+          <t>7.0%</t>
+        </is>
+      </c>
+      <c r="F20" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" s="13" t="inlineStr">
+        <is>
+          <t>10 ms</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="13" t="inlineStr">
+        <is>
+          <t>25 VUs</t>
+        </is>
+      </c>
+      <c r="B21" s="13" t="inlineStr">
+        <is>
+          <t>S06</t>
+        </is>
+      </c>
+      <c r="C21" s="12" t="inlineStr">
+        <is>
+          <t>Doctor Appointments List</t>
+        </is>
+      </c>
+      <c r="D21" s="13" t="inlineStr">
+        <is>
+          <t>160 MB</t>
+        </is>
+      </c>
+      <c r="E21" s="13" t="inlineStr">
+        <is>
+          <t>7.0%</t>
+        </is>
+      </c>
+      <c r="F21" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" s="13" t="inlineStr">
+        <is>
+          <t>10 ms</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="13" t="inlineStr">
+        <is>
+          <t>25 VUs</t>
+        </is>
+      </c>
+      <c r="B22" s="13" t="inlineStr">
+        <is>
+          <t>S07</t>
+        </is>
+      </c>
+      <c r="C22" s="12" t="inlineStr">
+        <is>
+          <t>Get Appointment Details</t>
+        </is>
+      </c>
+      <c r="D22" s="13" t="inlineStr">
+        <is>
+          <t>160 MB</t>
+        </is>
+      </c>
+      <c r="E22" s="13" t="inlineStr">
+        <is>
+          <t>7.0%</t>
+        </is>
+      </c>
+      <c r="F22" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" s="13" t="inlineStr">
+        <is>
+          <t>10 ms</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="13" t="inlineStr">
+        <is>
+          <t>25 VUs</t>
+        </is>
+      </c>
+      <c r="B23" s="13" t="inlineStr">
+        <is>
+          <t>S08</t>
+        </is>
+      </c>
+      <c r="C23" s="12" t="inlineStr">
+        <is>
+          <t>Queue Registration</t>
+        </is>
+      </c>
+      <c r="D23" s="13" t="inlineStr">
+        <is>
+          <t>160 MB</t>
+        </is>
+      </c>
+      <c r="E23" s="13" t="inlineStr">
+        <is>
+          <t>7.0%</t>
+        </is>
+      </c>
+      <c r="F23" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" s="13" t="n">
+        <v>25</v>
+      </c>
+      <c r="H23" s="13" t="inlineStr">
+        <is>
+          <t>10 ms</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="13" t="inlineStr">
+        <is>
+          <t>25 VUs</t>
+        </is>
+      </c>
+      <c r="B24" s="13" t="inlineStr">
+        <is>
+          <t>S09</t>
+        </is>
+      </c>
+      <c r="C24" s="12" t="inlineStr">
+        <is>
+          <t>Update Queue Status</t>
+        </is>
+      </c>
+      <c r="D24" s="13" t="inlineStr">
+        <is>
+          <t>160 MB</t>
+        </is>
+      </c>
+      <c r="E24" s="13" t="inlineStr">
+        <is>
+          <t>7.0%</t>
+        </is>
+      </c>
+      <c r="F24" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" s="13" t="n">
+        <v>25</v>
+      </c>
+      <c r="H24" s="13" t="inlineStr">
+        <is>
+          <t>10 ms</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="13" t="inlineStr">
+        <is>
+          <t>25 VUs</t>
+        </is>
+      </c>
+      <c r="B25" s="13" t="inlineStr">
+        <is>
+          <t>S10</t>
+        </is>
+      </c>
+      <c r="C25" s="12" t="inlineStr">
+        <is>
+          <t>Fetch Notifications</t>
+        </is>
+      </c>
+      <c r="D25" s="13" t="inlineStr">
+        <is>
+          <t>160 MB</t>
+        </is>
+      </c>
+      <c r="E25" s="13" t="inlineStr">
+        <is>
+          <t>7.0%</t>
+        </is>
+      </c>
+      <c r="F25" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" s="13" t="n">
+        <v>25</v>
+      </c>
+      <c r="H25" s="13" t="inlineStr">
+        <is>
+          <t>10 ms</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="13" t="inlineStr">
+        <is>
+          <t>25 VUs</t>
+        </is>
+      </c>
+      <c r="B26" s="13" t="inlineStr">
+        <is>
+          <t>S11</t>
+        </is>
+      </c>
+      <c r="C26" s="12" t="inlineStr">
+        <is>
+          <t>Submit Feedback</t>
+        </is>
+      </c>
+      <c r="D26" s="13" t="inlineStr">
+        <is>
+          <t>160 MB</t>
+        </is>
+      </c>
+      <c r="E26" s="13" t="inlineStr">
+        <is>
+          <t>7.0%</t>
+        </is>
+      </c>
+      <c r="F26" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" s="13" t="n">
+        <v>25</v>
+      </c>
+      <c r="H26" s="13" t="inlineStr">
+        <is>
+          <t>10 ms</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="13" t="inlineStr">
+        <is>
+          <t>25 VUs</t>
+        </is>
+      </c>
+      <c r="B27" s="13" t="inlineStr">
+        <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="C27" s="12" t="inlineStr">
+        <is>
+          <t>Upload Medical Record</t>
+        </is>
+      </c>
+      <c r="D27" s="13" t="inlineStr">
+        <is>
+          <t>170 MB</t>
+        </is>
+      </c>
+      <c r="E27" s="13" t="inlineStr">
+        <is>
+          <t>7.0%</t>
+        </is>
+      </c>
+      <c r="F27" s="13" t="n">
+        <v>50</v>
+      </c>
+      <c r="G27" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" s="13" t="inlineStr">
+        <is>
+          <t>10 ms</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="13" t="inlineStr">
+        <is>
+          <t>25 VUs</t>
+        </is>
+      </c>
+      <c r="B28" s="13" t="inlineStr">
+        <is>
+          <t>S13</t>
+        </is>
+      </c>
+      <c r="C28" s="12" t="inlineStr">
+        <is>
+          <t>Patient Dashboard Loading</t>
+        </is>
+      </c>
+      <c r="D28" s="13" t="inlineStr">
+        <is>
+          <t>160 MB</t>
+        </is>
+      </c>
+      <c r="E28" s="13" t="inlineStr">
+        <is>
+          <t>8.5%</t>
+        </is>
+      </c>
+      <c r="F28" s="13" t="n">
+        <v>50</v>
+      </c>
+      <c r="G28" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H28" s="13" t="inlineStr">
+        <is>
+          <t>10 ms</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="13" t="inlineStr">
+        <is>
+          <t>25 VUs</t>
+        </is>
+      </c>
+      <c r="B29" s="13" t="inlineStr">
+        <is>
+          <t>S14</t>
+        </is>
+      </c>
+      <c r="C29" s="12" t="inlineStr">
+        <is>
+          <t>Doctor Dashboard Loading</t>
+        </is>
+      </c>
+      <c r="D29" s="13" t="inlineStr">
+        <is>
+          <t>160 MB</t>
+        </is>
+      </c>
+      <c r="E29" s="13" t="inlineStr">
+        <is>
+          <t>7.0%</t>
+        </is>
+      </c>
+      <c r="F29" s="13" t="n">
+        <v>50</v>
+      </c>
+      <c r="G29" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" s="13" t="inlineStr">
+        <is>
+          <t>10 ms</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="13" t="inlineStr">
+        <is>
+          <t>50 VUs</t>
+        </is>
+      </c>
+      <c r="B30" s="13" t="inlineStr">
+        <is>
+          <t>S01</t>
+        </is>
+      </c>
+      <c r="C30" s="12" t="inlineStr">
+        <is>
+          <t>User Login</t>
+        </is>
+      </c>
+      <c r="D30" s="13" t="inlineStr">
+        <is>
+          <t>170 MB</t>
+        </is>
+      </c>
+      <c r="E30" s="13" t="inlineStr">
+        <is>
+          <t>9.0%</t>
+        </is>
+      </c>
+      <c r="F30" s="13" t="n">
+        <v>100</v>
+      </c>
+      <c r="G30" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" s="13" t="inlineStr">
+        <is>
+          <t>10 ms</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="13" t="inlineStr">
+        <is>
+          <t>50 VUs</t>
+        </is>
+      </c>
+      <c r="B31" s="13" t="inlineStr">
+        <is>
+          <t>S02</t>
+        </is>
+      </c>
+      <c r="C31" s="12" t="inlineStr">
+        <is>
+          <t>User Registration</t>
+        </is>
+      </c>
+      <c r="D31" s="13" t="inlineStr">
+        <is>
+          <t>170 MB</t>
+        </is>
+      </c>
+      <c r="E31" s="13" t="inlineStr">
+        <is>
+          <t>9.0%</t>
+        </is>
+      </c>
+      <c r="F31" s="13" t="n">
+        <v>100</v>
+      </c>
+      <c r="G31" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H31" s="13" t="inlineStr">
+        <is>
+          <t>10 ms</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="13" t="inlineStr">
+        <is>
+          <t>50 VUs</t>
+        </is>
+      </c>
+      <c r="B32" s="13" t="inlineStr">
+        <is>
+          <t>S03</t>
+        </is>
+      </c>
+      <c r="C32" s="12" t="inlineStr">
+        <is>
+          <t>Update Doctor Profile</t>
+        </is>
+      </c>
+      <c r="D32" s="13" t="inlineStr">
+        <is>
+          <t>170 MB</t>
+        </is>
+      </c>
+      <c r="E32" s="13" t="inlineStr">
+        <is>
+          <t>9.0%</t>
+        </is>
+      </c>
+      <c r="F32" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G32" s="13" t="n">
+        <v>50</v>
+      </c>
+      <c r="H32" s="13" t="inlineStr">
+        <is>
+          <t>10 ms</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="13" t="inlineStr">
+        <is>
+          <t>50 VUs</t>
+        </is>
+      </c>
+      <c r="B33" s="13" t="inlineStr">
+        <is>
+          <t>S04</t>
+        </is>
+      </c>
+      <c r="C33" s="12" t="inlineStr">
+        <is>
+          <t>Book Appointment</t>
+        </is>
+      </c>
+      <c r="D33" s="13" t="inlineStr">
+        <is>
+          <t>170 MB</t>
+        </is>
+      </c>
+      <c r="E33" s="13" t="inlineStr">
+        <is>
+          <t>9.0%</t>
+        </is>
+      </c>
+      <c r="F33" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G33" s="13" t="n">
+        <v>50</v>
+      </c>
+      <c r="H33" s="13" t="inlineStr">
+        <is>
+          <t>10 ms</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="13" t="inlineStr">
+        <is>
+          <t>50 VUs</t>
+        </is>
+      </c>
+      <c r="B34" s="13" t="inlineStr">
+        <is>
+          <t>S05</t>
+        </is>
+      </c>
+      <c r="C34" s="12" t="inlineStr">
+        <is>
+          <t>Patient Appointments List</t>
+        </is>
+      </c>
+      <c r="D34" s="13" t="inlineStr">
+        <is>
+          <t>170 MB</t>
+        </is>
+      </c>
+      <c r="E34" s="13" t="inlineStr">
+        <is>
+          <t>9.0%</t>
+        </is>
+      </c>
+      <c r="F34" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G34" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H34" s="13" t="inlineStr">
+        <is>
+          <t>10 ms</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="13" t="inlineStr">
+        <is>
+          <t>50 VUs</t>
+        </is>
+      </c>
+      <c r="B35" s="13" t="inlineStr">
+        <is>
+          <t>S06</t>
+        </is>
+      </c>
+      <c r="C35" s="12" t="inlineStr">
+        <is>
+          <t>Doctor Appointments List</t>
+        </is>
+      </c>
+      <c r="D35" s="13" t="inlineStr">
+        <is>
+          <t>170 MB</t>
+        </is>
+      </c>
+      <c r="E35" s="13" t="inlineStr">
+        <is>
+          <t>9.0%</t>
+        </is>
+      </c>
+      <c r="F35" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G35" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H35" s="13" t="inlineStr">
+        <is>
+          <t>10 ms</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="13" t="inlineStr">
+        <is>
+          <t>50 VUs</t>
+        </is>
+      </c>
+      <c r="B36" s="13" t="inlineStr">
+        <is>
+          <t>S07</t>
+        </is>
+      </c>
+      <c r="C36" s="12" t="inlineStr">
+        <is>
+          <t>Get Appointment Details</t>
+        </is>
+      </c>
+      <c r="D36" s="13" t="inlineStr">
+        <is>
+          <t>170 MB</t>
+        </is>
+      </c>
+      <c r="E36" s="13" t="inlineStr">
+        <is>
+          <t>9.0%</t>
+        </is>
+      </c>
+      <c r="F36" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G36" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H36" s="13" t="inlineStr">
+        <is>
+          <t>10 ms</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="13" t="inlineStr">
+        <is>
+          <t>50 VUs</t>
+        </is>
+      </c>
+      <c r="B37" s="13" t="inlineStr">
+        <is>
+          <t>S08</t>
+        </is>
+      </c>
+      <c r="C37" s="12" t="inlineStr">
+        <is>
+          <t>Queue Registration</t>
+        </is>
+      </c>
+      <c r="D37" s="13" t="inlineStr">
+        <is>
+          <t>170 MB</t>
+        </is>
+      </c>
+      <c r="E37" s="13" t="inlineStr">
+        <is>
+          <t>9.0%</t>
+        </is>
+      </c>
+      <c r="F37" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G37" s="13" t="n">
+        <v>50</v>
+      </c>
+      <c r="H37" s="13" t="inlineStr">
+        <is>
+          <t>10 ms</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="13" t="inlineStr">
+        <is>
+          <t>50 VUs</t>
+        </is>
+      </c>
+      <c r="B38" s="13" t="inlineStr">
+        <is>
+          <t>S09</t>
+        </is>
+      </c>
+      <c r="C38" s="12" t="inlineStr">
+        <is>
+          <t>Update Queue Status</t>
+        </is>
+      </c>
+      <c r="D38" s="13" t="inlineStr">
+        <is>
+          <t>170 MB</t>
+        </is>
+      </c>
+      <c r="E38" s="13" t="inlineStr">
+        <is>
+          <t>9.0%</t>
+        </is>
+      </c>
+      <c r="F38" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G38" s="13" t="n">
+        <v>50</v>
+      </c>
+      <c r="H38" s="13" t="inlineStr">
+        <is>
+          <t>10 ms</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="13" t="inlineStr">
+        <is>
+          <t>50 VUs</t>
+        </is>
+      </c>
+      <c r="B39" s="13" t="inlineStr">
+        <is>
+          <t>S10</t>
+        </is>
+      </c>
+      <c r="C39" s="12" t="inlineStr">
+        <is>
+          <t>Fetch Notifications</t>
+        </is>
+      </c>
+      <c r="D39" s="13" t="inlineStr">
+        <is>
+          <t>170 MB</t>
+        </is>
+      </c>
+      <c r="E39" s="13" t="inlineStr">
+        <is>
+          <t>9.0%</t>
+        </is>
+      </c>
+      <c r="F39" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G39" s="13" t="n">
+        <v>50</v>
+      </c>
+      <c r="H39" s="13" t="inlineStr">
+        <is>
+          <t>10 ms</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="13" t="inlineStr">
+        <is>
+          <t>50 VUs</t>
+        </is>
+      </c>
+      <c r="B40" s="13" t="inlineStr">
+        <is>
+          <t>S11</t>
+        </is>
+      </c>
+      <c r="C40" s="12" t="inlineStr">
+        <is>
+          <t>Submit Feedback</t>
+        </is>
+      </c>
+      <c r="D40" s="13" t="inlineStr">
+        <is>
+          <t>170 MB</t>
+        </is>
+      </c>
+      <c r="E40" s="13" t="inlineStr">
+        <is>
+          <t>9.0%</t>
+        </is>
+      </c>
+      <c r="F40" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G40" s="13" t="n">
+        <v>50</v>
+      </c>
+      <c r="H40" s="13" t="inlineStr">
+        <is>
+          <t>10 ms</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="13" t="inlineStr">
+        <is>
+          <t>50 VUs</t>
+        </is>
+      </c>
+      <c r="B41" s="13" t="inlineStr">
+        <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="C41" s="12" t="inlineStr">
+        <is>
+          <t>Upload Medical Record</t>
+        </is>
+      </c>
+      <c r="D41" s="13" t="inlineStr">
+        <is>
+          <t>180 MB</t>
+        </is>
+      </c>
+      <c r="E41" s="13" t="inlineStr">
+        <is>
+          <t>9.0%</t>
+        </is>
+      </c>
+      <c r="F41" s="13" t="n">
+        <v>100</v>
+      </c>
+      <c r="G41" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H41" s="13" t="inlineStr">
+        <is>
+          <t>10 ms</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="13" t="inlineStr">
+        <is>
+          <t>50 VUs</t>
+        </is>
+      </c>
+      <c r="B42" s="13" t="inlineStr">
+        <is>
+          <t>S13</t>
+        </is>
+      </c>
+      <c r="C42" s="12" t="inlineStr">
+        <is>
+          <t>Patient Dashboard Loading</t>
+        </is>
+      </c>
+      <c r="D42" s="13" t="inlineStr">
+        <is>
+          <t>170 MB</t>
+        </is>
+      </c>
+      <c r="E42" s="13" t="inlineStr">
+        <is>
+          <t>10.5%</t>
+        </is>
+      </c>
+      <c r="F42" s="13" t="n">
+        <v>100</v>
+      </c>
+      <c r="G42" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H42" s="13" t="inlineStr">
+        <is>
+          <t>10 ms</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="13" t="inlineStr">
+        <is>
+          <t>50 VUs</t>
+        </is>
+      </c>
+      <c r="B43" s="13" t="inlineStr">
+        <is>
+          <t>S14</t>
+        </is>
+      </c>
+      <c r="C43" s="12" t="inlineStr">
+        <is>
+          <t>Doctor Dashboard Loading</t>
+        </is>
+      </c>
+      <c r="D43" s="13" t="inlineStr">
+        <is>
+          <t>170 MB</t>
+        </is>
+      </c>
+      <c r="E43" s="13" t="inlineStr">
+        <is>
+          <t>9.0%</t>
+        </is>
+      </c>
+      <c r="F43" s="13" t="n">
+        <v>100</v>
+      </c>
+      <c r="G43" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H43" s="13" t="inlineStr">
+        <is>
+          <t>10 ms</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="13" t="inlineStr">
+        <is>
+          <t>100 VUs</t>
+        </is>
+      </c>
+      <c r="B44" s="13" t="inlineStr">
+        <is>
+          <t>S01</t>
+        </is>
+      </c>
+      <c r="C44" s="12" t="inlineStr">
+        <is>
+          <t>User Login</t>
+        </is>
+      </c>
+      <c r="D44" s="13" t="inlineStr">
+        <is>
+          <t>190 MB</t>
+        </is>
+      </c>
+      <c r="E44" s="13" t="inlineStr">
+        <is>
+          <t>13.0%</t>
+        </is>
+      </c>
+      <c r="F44" s="13" t="n">
+        <v>200</v>
+      </c>
+      <c r="G44" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H44" s="13" t="inlineStr">
+        <is>
+          <t>10 ms</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="13" t="inlineStr">
+        <is>
+          <t>100 VUs</t>
+        </is>
+      </c>
+      <c r="B45" s="13" t="inlineStr">
+        <is>
+          <t>S02</t>
+        </is>
+      </c>
+      <c r="C45" s="12" t="inlineStr">
+        <is>
+          <t>User Registration</t>
+        </is>
+      </c>
+      <c r="D45" s="13" t="inlineStr">
+        <is>
+          <t>190 MB</t>
+        </is>
+      </c>
+      <c r="E45" s="13" t="inlineStr">
+        <is>
+          <t>13.0%</t>
+        </is>
+      </c>
+      <c r="F45" s="13" t="n">
+        <v>200</v>
+      </c>
+      <c r="G45" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H45" s="13" t="inlineStr">
+        <is>
+          <t>10 ms</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="13" t="inlineStr">
+        <is>
+          <t>100 VUs</t>
+        </is>
+      </c>
+      <c r="B46" s="13" t="inlineStr">
+        <is>
+          <t>S03</t>
+        </is>
+      </c>
+      <c r="C46" s="12" t="inlineStr">
+        <is>
+          <t>Update Doctor Profile</t>
+        </is>
+      </c>
+      <c r="D46" s="13" t="inlineStr">
+        <is>
+          <t>190 MB</t>
+        </is>
+      </c>
+      <c r="E46" s="13" t="inlineStr">
+        <is>
+          <t>13.0%</t>
+        </is>
+      </c>
+      <c r="F46" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G46" s="13" t="n">
+        <v>100</v>
+      </c>
+      <c r="H46" s="13" t="inlineStr">
+        <is>
+          <t>10 ms</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="13" t="inlineStr">
+        <is>
+          <t>100 VUs</t>
+        </is>
+      </c>
+      <c r="B47" s="13" t="inlineStr">
+        <is>
+          <t>S04</t>
+        </is>
+      </c>
+      <c r="C47" s="12" t="inlineStr">
+        <is>
+          <t>Book Appointment</t>
+        </is>
+      </c>
+      <c r="D47" s="13" t="inlineStr">
+        <is>
+          <t>190 MB</t>
+        </is>
+      </c>
+      <c r="E47" s="13" t="inlineStr">
+        <is>
+          <t>13.0%</t>
+        </is>
+      </c>
+      <c r="F47" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G47" s="13" t="n">
+        <v>100</v>
+      </c>
+      <c r="H47" s="13" t="inlineStr">
+        <is>
+          <t>10 ms</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="13" t="inlineStr">
+        <is>
+          <t>100 VUs</t>
+        </is>
+      </c>
+      <c r="B48" s="13" t="inlineStr">
+        <is>
+          <t>S05</t>
+        </is>
+      </c>
+      <c r="C48" s="12" t="inlineStr">
+        <is>
+          <t>Patient Appointments List</t>
+        </is>
+      </c>
+      <c r="D48" s="13" t="inlineStr">
+        <is>
+          <t>190 MB</t>
+        </is>
+      </c>
+      <c r="E48" s="13" t="inlineStr">
+        <is>
+          <t>13.0%</t>
+        </is>
+      </c>
+      <c r="F48" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G48" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H48" s="13" t="inlineStr">
+        <is>
+          <t>10 ms</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="13" t="inlineStr">
+        <is>
+          <t>100 VUs</t>
+        </is>
+      </c>
+      <c r="B49" s="13" t="inlineStr">
+        <is>
+          <t>S06</t>
+        </is>
+      </c>
+      <c r="C49" s="12" t="inlineStr">
+        <is>
+          <t>Doctor Appointments List</t>
+        </is>
+      </c>
+      <c r="D49" s="13" t="inlineStr">
+        <is>
+          <t>190 MB</t>
+        </is>
+      </c>
+      <c r="E49" s="13" t="inlineStr">
+        <is>
+          <t>13.0%</t>
+        </is>
+      </c>
+      <c r="F49" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G49" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H49" s="13" t="inlineStr">
+        <is>
+          <t>10 ms</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="13" t="inlineStr">
+        <is>
+          <t>100 VUs</t>
+        </is>
+      </c>
+      <c r="B50" s="13" t="inlineStr">
+        <is>
+          <t>S07</t>
+        </is>
+      </c>
+      <c r="C50" s="12" t="inlineStr">
+        <is>
+          <t>Get Appointment Details</t>
+        </is>
+      </c>
+      <c r="D50" s="13" t="inlineStr">
+        <is>
+          <t>190 MB</t>
+        </is>
+      </c>
+      <c r="E50" s="13" t="inlineStr">
+        <is>
+          <t>13.0%</t>
+        </is>
+      </c>
+      <c r="F50" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G50" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H50" s="13" t="inlineStr">
+        <is>
+          <t>10 ms</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="13" t="inlineStr">
+        <is>
+          <t>100 VUs</t>
+        </is>
+      </c>
+      <c r="B51" s="13" t="inlineStr">
+        <is>
+          <t>S08</t>
+        </is>
+      </c>
+      <c r="C51" s="12" t="inlineStr">
+        <is>
+          <t>Queue Registration</t>
+        </is>
+      </c>
+      <c r="D51" s="13" t="inlineStr">
+        <is>
+          <t>190 MB</t>
+        </is>
+      </c>
+      <c r="E51" s="13" t="inlineStr">
+        <is>
+          <t>13.0%</t>
+        </is>
+      </c>
+      <c r="F51" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G51" s="13" t="n">
+        <v>100</v>
+      </c>
+      <c r="H51" s="13" t="inlineStr">
+        <is>
+          <t>10 ms</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="13" t="inlineStr">
+        <is>
+          <t>100 VUs</t>
+        </is>
+      </c>
+      <c r="B52" s="13" t="inlineStr">
+        <is>
+          <t>S09</t>
+        </is>
+      </c>
+      <c r="C52" s="12" t="inlineStr">
+        <is>
+          <t>Update Queue Status</t>
+        </is>
+      </c>
+      <c r="D52" s="13" t="inlineStr">
+        <is>
+          <t>190 MB</t>
+        </is>
+      </c>
+      <c r="E52" s="13" t="inlineStr">
+        <is>
+          <t>13.0%</t>
+        </is>
+      </c>
+      <c r="F52" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G52" s="13" t="n">
+        <v>100</v>
+      </c>
+      <c r="H52" s="13" t="inlineStr">
+        <is>
+          <t>10 ms</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="13" t="inlineStr">
+        <is>
+          <t>100 VUs</t>
+        </is>
+      </c>
+      <c r="B53" s="13" t="inlineStr">
+        <is>
+          <t>S10</t>
+        </is>
+      </c>
+      <c r="C53" s="12" t="inlineStr">
+        <is>
+          <t>Fetch Notifications</t>
+        </is>
+      </c>
+      <c r="D53" s="13" t="inlineStr">
+        <is>
+          <t>190 MB</t>
+        </is>
+      </c>
+      <c r="E53" s="13" t="inlineStr">
+        <is>
+          <t>13.0%</t>
+        </is>
+      </c>
+      <c r="F53" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G53" s="13" t="n">
+        <v>100</v>
+      </c>
+      <c r="H53" s="13" t="inlineStr">
+        <is>
+          <t>10 ms</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="13" t="inlineStr">
+        <is>
+          <t>100 VUs</t>
+        </is>
+      </c>
+      <c r="B54" s="13" t="inlineStr">
+        <is>
+          <t>S11</t>
+        </is>
+      </c>
+      <c r="C54" s="12" t="inlineStr">
+        <is>
+          <t>Submit Feedback</t>
+        </is>
+      </c>
+      <c r="D54" s="13" t="inlineStr">
+        <is>
+          <t>190 MB</t>
+        </is>
+      </c>
+      <c r="E54" s="13" t="inlineStr">
+        <is>
+          <t>13.0%</t>
+        </is>
+      </c>
+      <c r="F54" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G54" s="13" t="n">
+        <v>100</v>
+      </c>
+      <c r="H54" s="13" t="inlineStr">
+        <is>
+          <t>10 ms</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="13" t="inlineStr">
+        <is>
+          <t>100 VUs</t>
+        </is>
+      </c>
+      <c r="B55" s="13" t="inlineStr">
+        <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="C55" s="12" t="inlineStr">
+        <is>
+          <t>Upload Medical Record</t>
+        </is>
+      </c>
+      <c r="D55" s="13" t="inlineStr">
+        <is>
+          <t>200 MB</t>
+        </is>
+      </c>
+      <c r="E55" s="13" t="inlineStr">
+        <is>
+          <t>13.0%</t>
+        </is>
+      </c>
+      <c r="F55" s="13" t="n">
+        <v>200</v>
+      </c>
+      <c r="G55" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H55" s="13" t="inlineStr">
+        <is>
+          <t>10 ms</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="13" t="inlineStr">
+        <is>
+          <t>100 VUs</t>
+        </is>
+      </c>
+      <c r="B56" s="13" t="inlineStr">
+        <is>
+          <t>S13</t>
+        </is>
+      </c>
+      <c r="C56" s="12" t="inlineStr">
+        <is>
+          <t>Patient Dashboard Loading</t>
+        </is>
+      </c>
+      <c r="D56" s="13" t="inlineStr">
+        <is>
+          <t>190 MB</t>
+        </is>
+      </c>
+      <c r="E56" s="13" t="inlineStr">
+        <is>
+          <t>14.5%</t>
+        </is>
+      </c>
+      <c r="F56" s="13" t="n">
+        <v>200</v>
+      </c>
+      <c r="G56" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H56" s="13" t="inlineStr">
+        <is>
+          <t>10 ms</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="13" t="inlineStr">
+        <is>
+          <t>100 VUs</t>
+        </is>
+      </c>
+      <c r="B57" s="13" t="inlineStr">
+        <is>
+          <t>S14</t>
+        </is>
+      </c>
+      <c r="C57" s="12" t="inlineStr">
+        <is>
+          <t>Doctor Dashboard Loading</t>
+        </is>
+      </c>
+      <c r="D57" s="13" t="inlineStr">
+        <is>
+          <t>190 MB</t>
+        </is>
+      </c>
+      <c r="E57" s="13" t="inlineStr">
+        <is>
+          <t>13.0%</t>
+        </is>
+      </c>
+      <c r="F57" s="13" t="n">
+        <v>200</v>
+      </c>
+      <c r="G57" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H57" s="13" t="inlineStr">
+        <is>
+          <t>10 ms</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="13" t="inlineStr">
+        <is>
+          <t>250 VUs</t>
+        </is>
+      </c>
+      <c r="B58" s="13" t="inlineStr">
+        <is>
+          <t>S01</t>
+        </is>
+      </c>
+      <c r="C58" s="12" t="inlineStr">
+        <is>
+          <t>User Login</t>
+        </is>
+      </c>
+      <c r="D58" s="13" t="inlineStr">
+        <is>
+          <t>250 MB</t>
+        </is>
+      </c>
+      <c r="E58" s="13" t="inlineStr">
+        <is>
+          <t>25.0%</t>
+        </is>
+      </c>
+      <c r="F58" s="13" t="n">
+        <v>500</v>
+      </c>
+      <c r="G58" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H58" s="13" t="inlineStr">
+        <is>
+          <t>11 ms</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="13" t="inlineStr">
+        <is>
+          <t>250 VUs</t>
+        </is>
+      </c>
+      <c r="B59" s="13" t="inlineStr">
+        <is>
+          <t>S02</t>
+        </is>
+      </c>
+      <c r="C59" s="12" t="inlineStr">
+        <is>
+          <t>User Registration</t>
+        </is>
+      </c>
+      <c r="D59" s="13" t="inlineStr">
+        <is>
+          <t>250 MB</t>
+        </is>
+      </c>
+      <c r="E59" s="13" t="inlineStr">
+        <is>
+          <t>25.0%</t>
+        </is>
+      </c>
+      <c r="F59" s="13" t="n">
+        <v>500</v>
+      </c>
+      <c r="G59" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H59" s="13" t="inlineStr">
+        <is>
+          <t>11 ms</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="13" t="inlineStr">
+        <is>
+          <t>250 VUs</t>
+        </is>
+      </c>
+      <c r="B60" s="13" t="inlineStr">
+        <is>
+          <t>S03</t>
+        </is>
+      </c>
+      <c r="C60" s="12" t="inlineStr">
+        <is>
+          <t>Update Doctor Profile</t>
+        </is>
+      </c>
+      <c r="D60" s="13" t="inlineStr">
+        <is>
+          <t>250 MB</t>
+        </is>
+      </c>
+      <c r="E60" s="13" t="inlineStr">
+        <is>
+          <t>25.0%</t>
+        </is>
+      </c>
+      <c r="F60" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G60" s="13" t="n">
+        <v>250</v>
+      </c>
+      <c r="H60" s="13" t="inlineStr">
+        <is>
+          <t>11 ms</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="13" t="inlineStr">
+        <is>
+          <t>250 VUs</t>
+        </is>
+      </c>
+      <c r="B61" s="13" t="inlineStr">
+        <is>
+          <t>S04</t>
+        </is>
+      </c>
+      <c r="C61" s="12" t="inlineStr">
+        <is>
+          <t>Book Appointment</t>
+        </is>
+      </c>
+      <c r="D61" s="13" t="inlineStr">
+        <is>
+          <t>250 MB</t>
+        </is>
+      </c>
+      <c r="E61" s="13" t="inlineStr">
+        <is>
+          <t>25.0%</t>
+        </is>
+      </c>
+      <c r="F61" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G61" s="13" t="n">
+        <v>250</v>
+      </c>
+      <c r="H61" s="13" t="inlineStr">
+        <is>
+          <t>11 ms</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="13" t="inlineStr">
+        <is>
+          <t>250 VUs</t>
+        </is>
+      </c>
+      <c r="B62" s="13" t="inlineStr">
+        <is>
+          <t>S05</t>
+        </is>
+      </c>
+      <c r="C62" s="12" t="inlineStr">
+        <is>
+          <t>Patient Appointments List</t>
+        </is>
+      </c>
+      <c r="D62" s="13" t="inlineStr">
+        <is>
+          <t>250 MB</t>
+        </is>
+      </c>
+      <c r="E62" s="13" t="inlineStr">
+        <is>
+          <t>25.0%</t>
+        </is>
+      </c>
+      <c r="F62" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G62" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H62" s="13" t="inlineStr">
+        <is>
+          <t>11 ms</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="13" t="inlineStr">
+        <is>
+          <t>250 VUs</t>
+        </is>
+      </c>
+      <c r="B63" s="13" t="inlineStr">
+        <is>
+          <t>S06</t>
+        </is>
+      </c>
+      <c r="C63" s="12" t="inlineStr">
+        <is>
+          <t>Doctor Appointments List</t>
+        </is>
+      </c>
+      <c r="D63" s="13" t="inlineStr">
+        <is>
+          <t>250 MB</t>
+        </is>
+      </c>
+      <c r="E63" s="13" t="inlineStr">
+        <is>
+          <t>25.0%</t>
+        </is>
+      </c>
+      <c r="F63" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G63" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H63" s="13" t="inlineStr">
+        <is>
+          <t>11 ms</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="13" t="inlineStr">
+        <is>
+          <t>250 VUs</t>
+        </is>
+      </c>
+      <c r="B64" s="13" t="inlineStr">
+        <is>
+          <t>S07</t>
+        </is>
+      </c>
+      <c r="C64" s="12" t="inlineStr">
+        <is>
+          <t>Get Appointment Details</t>
+        </is>
+      </c>
+      <c r="D64" s="13" t="inlineStr">
+        <is>
+          <t>250 MB</t>
+        </is>
+      </c>
+      <c r="E64" s="13" t="inlineStr">
+        <is>
+          <t>25.0%</t>
+        </is>
+      </c>
+      <c r="F64" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G64" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H64" s="13" t="inlineStr">
+        <is>
+          <t>11 ms</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="13" t="inlineStr">
+        <is>
+          <t>250 VUs</t>
+        </is>
+      </c>
+      <c r="B65" s="13" t="inlineStr">
+        <is>
+          <t>S08</t>
+        </is>
+      </c>
+      <c r="C65" s="12" t="inlineStr">
+        <is>
+          <t>Queue Registration</t>
+        </is>
+      </c>
+      <c r="D65" s="13" t="inlineStr">
+        <is>
+          <t>250 MB</t>
+        </is>
+      </c>
+      <c r="E65" s="13" t="inlineStr">
+        <is>
+          <t>25.0%</t>
+        </is>
+      </c>
+      <c r="F65" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G65" s="13" t="n">
+        <v>250</v>
+      </c>
+      <c r="H65" s="13" t="inlineStr">
+        <is>
+          <t>11 ms</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="13" t="inlineStr">
+        <is>
+          <t>250 VUs</t>
+        </is>
+      </c>
+      <c r="B66" s="13" t="inlineStr">
+        <is>
+          <t>S09</t>
+        </is>
+      </c>
+      <c r="C66" s="12" t="inlineStr">
+        <is>
+          <t>Update Queue Status</t>
+        </is>
+      </c>
+      <c r="D66" s="13" t="inlineStr">
+        <is>
+          <t>250 MB</t>
+        </is>
+      </c>
+      <c r="E66" s="13" t="inlineStr">
+        <is>
+          <t>25.0%</t>
+        </is>
+      </c>
+      <c r="F66" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G66" s="13" t="n">
+        <v>250</v>
+      </c>
+      <c r="H66" s="13" t="inlineStr">
+        <is>
+          <t>11 ms</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="13" t="inlineStr">
+        <is>
+          <t>250 VUs</t>
+        </is>
+      </c>
+      <c r="B67" s="13" t="inlineStr">
+        <is>
+          <t>S10</t>
+        </is>
+      </c>
+      <c r="C67" s="12" t="inlineStr">
+        <is>
+          <t>Fetch Notifications</t>
+        </is>
+      </c>
+      <c r="D67" s="13" t="inlineStr">
+        <is>
+          <t>250 MB</t>
+        </is>
+      </c>
+      <c r="E67" s="13" t="inlineStr">
+        <is>
+          <t>25.0%</t>
+        </is>
+      </c>
+      <c r="F67" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G67" s="13" t="n">
+        <v>250</v>
+      </c>
+      <c r="H67" s="13" t="inlineStr">
+        <is>
+          <t>11 ms</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="13" t="inlineStr">
+        <is>
+          <t>250 VUs</t>
+        </is>
+      </c>
+      <c r="B68" s="13" t="inlineStr">
+        <is>
+          <t>S11</t>
+        </is>
+      </c>
+      <c r="C68" s="12" t="inlineStr">
+        <is>
+          <t>Submit Feedback</t>
+        </is>
+      </c>
+      <c r="D68" s="13" t="inlineStr">
+        <is>
+          <t>250 MB</t>
+        </is>
+      </c>
+      <c r="E68" s="13" t="inlineStr">
+        <is>
+          <t>25.0%</t>
+        </is>
+      </c>
+      <c r="F68" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G68" s="13" t="n">
+        <v>250</v>
+      </c>
+      <c r="H68" s="13" t="inlineStr">
+        <is>
+          <t>11 ms</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="13" t="inlineStr">
+        <is>
+          <t>250 VUs</t>
+        </is>
+      </c>
+      <c r="B69" s="13" t="inlineStr">
+        <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="C69" s="12" t="inlineStr">
+        <is>
+          <t>Upload Medical Record</t>
+        </is>
+      </c>
+      <c r="D69" s="13" t="inlineStr">
+        <is>
+          <t>260 MB</t>
+        </is>
+      </c>
+      <c r="E69" s="13" t="inlineStr">
+        <is>
+          <t>25.0%</t>
+        </is>
+      </c>
+      <c r="F69" s="13" t="n">
+        <v>500</v>
+      </c>
+      <c r="G69" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H69" s="13" t="inlineStr">
+        <is>
+          <t>11 ms</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="13" t="inlineStr">
+        <is>
+          <t>250 VUs</t>
+        </is>
+      </c>
+      <c r="B70" s="13" t="inlineStr">
+        <is>
+          <t>S13</t>
+        </is>
+      </c>
+      <c r="C70" s="12" t="inlineStr">
+        <is>
+          <t>Patient Dashboard Loading</t>
+        </is>
+      </c>
+      <c r="D70" s="13" t="inlineStr">
+        <is>
+          <t>250 MB</t>
+        </is>
+      </c>
+      <c r="E70" s="13" t="inlineStr">
+        <is>
+          <t>26.5%</t>
+        </is>
+      </c>
+      <c r="F70" s="13" t="n">
+        <v>500</v>
+      </c>
+      <c r="G70" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H70" s="13" t="inlineStr">
+        <is>
+          <t>11 ms</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="13" t="inlineStr">
+        <is>
+          <t>250 VUs</t>
+        </is>
+      </c>
+      <c r="B71" s="13" t="inlineStr">
+        <is>
+          <t>S14</t>
+        </is>
+      </c>
+      <c r="C71" s="12" t="inlineStr">
+        <is>
+          <t>Doctor Dashboard Loading</t>
+        </is>
+      </c>
+      <c r="D71" s="13" t="inlineStr">
+        <is>
+          <t>250 MB</t>
+        </is>
+      </c>
+      <c r="E71" s="13" t="inlineStr">
+        <is>
+          <t>25.0%</t>
+        </is>
+      </c>
+      <c r="F71" s="13" t="n">
+        <v>500</v>
+      </c>
+      <c r="G71" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H71" s="13" t="inlineStr">
+        <is>
+          <t>11 ms</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="13" t="inlineStr">
+        <is>
+          <t>500 VUs</t>
+        </is>
+      </c>
+      <c r="B72" s="13" t="inlineStr">
+        <is>
+          <t>S01</t>
+        </is>
+      </c>
+      <c r="C72" s="12" t="inlineStr">
+        <is>
+          <t>User Login</t>
+        </is>
+      </c>
+      <c r="D72" s="13" t="inlineStr">
+        <is>
+          <t>350 MB</t>
+        </is>
+      </c>
+      <c r="E72" s="13" t="inlineStr">
+        <is>
+          <t>45.0%</t>
+        </is>
+      </c>
+      <c r="F72" s="13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="G72" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H72" s="13" t="inlineStr">
+        <is>
+          <t>13 ms</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="13" t="inlineStr">
+        <is>
+          <t>500 VUs</t>
+        </is>
+      </c>
+      <c r="B73" s="13" t="inlineStr">
+        <is>
+          <t>S02</t>
+        </is>
+      </c>
+      <c r="C73" s="12" t="inlineStr">
+        <is>
+          <t>User Registration</t>
+        </is>
+      </c>
+      <c r="D73" s="13" t="inlineStr">
+        <is>
+          <t>350 MB</t>
+        </is>
+      </c>
+      <c r="E73" s="13" t="inlineStr">
+        <is>
+          <t>45.0%</t>
+        </is>
+      </c>
+      <c r="F73" s="13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="G73" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H73" s="13" t="inlineStr">
+        <is>
+          <t>13 ms</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="13" t="inlineStr">
+        <is>
+          <t>500 VUs</t>
+        </is>
+      </c>
+      <c r="B74" s="13" t="inlineStr">
+        <is>
+          <t>S03</t>
+        </is>
+      </c>
+      <c r="C74" s="12" t="inlineStr">
+        <is>
+          <t>Update Doctor Profile</t>
+        </is>
+      </c>
+      <c r="D74" s="13" t="inlineStr">
+        <is>
+          <t>350 MB</t>
+        </is>
+      </c>
+      <c r="E74" s="13" t="inlineStr">
+        <is>
+          <t>45.0%</t>
+        </is>
+      </c>
+      <c r="F74" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G74" s="13" t="n">
+        <v>500</v>
+      </c>
+      <c r="H74" s="13" t="inlineStr">
+        <is>
+          <t>13 ms</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="13" t="inlineStr">
+        <is>
+          <t>500 VUs</t>
+        </is>
+      </c>
+      <c r="B75" s="13" t="inlineStr">
+        <is>
+          <t>S04</t>
+        </is>
+      </c>
+      <c r="C75" s="12" t="inlineStr">
+        <is>
+          <t>Book Appointment</t>
+        </is>
+      </c>
+      <c r="D75" s="13" t="inlineStr">
+        <is>
+          <t>350 MB</t>
+        </is>
+      </c>
+      <c r="E75" s="13" t="inlineStr">
+        <is>
+          <t>45.0%</t>
+        </is>
+      </c>
+      <c r="F75" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G75" s="13" t="n">
+        <v>500</v>
+      </c>
+      <c r="H75" s="13" t="inlineStr">
+        <is>
+          <t>13 ms</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="13" t="inlineStr">
+        <is>
+          <t>500 VUs</t>
+        </is>
+      </c>
+      <c r="B76" s="13" t="inlineStr">
+        <is>
+          <t>S05</t>
+        </is>
+      </c>
+      <c r="C76" s="12" t="inlineStr">
+        <is>
+          <t>Patient Appointments List</t>
+        </is>
+      </c>
+      <c r="D76" s="13" t="inlineStr">
+        <is>
+          <t>350 MB</t>
+        </is>
+      </c>
+      <c r="E76" s="13" t="inlineStr">
+        <is>
+          <t>45.0%</t>
+        </is>
+      </c>
+      <c r="F76" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G76" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H76" s="13" t="inlineStr">
+        <is>
+          <t>13 ms</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="13" t="inlineStr">
+        <is>
+          <t>500 VUs</t>
+        </is>
+      </c>
+      <c r="B77" s="13" t="inlineStr">
+        <is>
+          <t>S06</t>
+        </is>
+      </c>
+      <c r="C77" s="12" t="inlineStr">
+        <is>
+          <t>Doctor Appointments List</t>
+        </is>
+      </c>
+      <c r="D77" s="13" t="inlineStr">
+        <is>
+          <t>350 MB</t>
+        </is>
+      </c>
+      <c r="E77" s="13" t="inlineStr">
+        <is>
+          <t>45.0%</t>
+        </is>
+      </c>
+      <c r="F77" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G77" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H77" s="13" t="inlineStr">
+        <is>
+          <t>13 ms</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="13" t="inlineStr">
+        <is>
+          <t>500 VUs</t>
+        </is>
+      </c>
+      <c r="B78" s="13" t="inlineStr">
+        <is>
+          <t>S07</t>
+        </is>
+      </c>
+      <c r="C78" s="12" t="inlineStr">
+        <is>
+          <t>Get Appointment Details</t>
+        </is>
+      </c>
+      <c r="D78" s="13" t="inlineStr">
+        <is>
+          <t>350 MB</t>
+        </is>
+      </c>
+      <c r="E78" s="13" t="inlineStr">
+        <is>
+          <t>45.0%</t>
+        </is>
+      </c>
+      <c r="F78" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G78" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H78" s="13" t="inlineStr">
+        <is>
+          <t>13 ms</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="13" t="inlineStr">
+        <is>
+          <t>500 VUs</t>
+        </is>
+      </c>
+      <c r="B79" s="13" t="inlineStr">
+        <is>
+          <t>S08</t>
+        </is>
+      </c>
+      <c r="C79" s="12" t="inlineStr">
+        <is>
+          <t>Queue Registration</t>
+        </is>
+      </c>
+      <c r="D79" s="13" t="inlineStr">
+        <is>
+          <t>350 MB</t>
+        </is>
+      </c>
+      <c r="E79" s="13" t="inlineStr">
+        <is>
+          <t>45.0%</t>
+        </is>
+      </c>
+      <c r="F79" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G79" s="13" t="n">
+        <v>500</v>
+      </c>
+      <c r="H79" s="13" t="inlineStr">
+        <is>
+          <t>13 ms</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="13" t="inlineStr">
+        <is>
+          <t>500 VUs</t>
+        </is>
+      </c>
+      <c r="B80" s="13" t="inlineStr">
+        <is>
+          <t>S09</t>
+        </is>
+      </c>
+      <c r="C80" s="12" t="inlineStr">
+        <is>
+          <t>Update Queue Status</t>
+        </is>
+      </c>
+      <c r="D80" s="13" t="inlineStr">
+        <is>
+          <t>350 MB</t>
+        </is>
+      </c>
+      <c r="E80" s="13" t="inlineStr">
+        <is>
+          <t>45.0%</t>
+        </is>
+      </c>
+      <c r="F80" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G80" s="13" t="n">
+        <v>500</v>
+      </c>
+      <c r="H80" s="13" t="inlineStr">
+        <is>
+          <t>13 ms</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="13" t="inlineStr">
+        <is>
+          <t>500 VUs</t>
+        </is>
+      </c>
+      <c r="B81" s="13" t="inlineStr">
+        <is>
+          <t>S10</t>
+        </is>
+      </c>
+      <c r="C81" s="12" t="inlineStr">
+        <is>
+          <t>Fetch Notifications</t>
+        </is>
+      </c>
+      <c r="D81" s="13" t="inlineStr">
+        <is>
+          <t>350 MB</t>
+        </is>
+      </c>
+      <c r="E81" s="13" t="inlineStr">
+        <is>
+          <t>45.0%</t>
+        </is>
+      </c>
+      <c r="F81" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G81" s="13" t="n">
+        <v>500</v>
+      </c>
+      <c r="H81" s="13" t="inlineStr">
+        <is>
+          <t>13 ms</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="13" t="inlineStr">
+        <is>
+          <t>500 VUs</t>
+        </is>
+      </c>
+      <c r="B82" s="13" t="inlineStr">
+        <is>
+          <t>S11</t>
+        </is>
+      </c>
+      <c r="C82" s="12" t="inlineStr">
+        <is>
+          <t>Submit Feedback</t>
+        </is>
+      </c>
+      <c r="D82" s="13" t="inlineStr">
+        <is>
+          <t>350 MB</t>
+        </is>
+      </c>
+      <c r="E82" s="13" t="inlineStr">
+        <is>
+          <t>45.0%</t>
+        </is>
+      </c>
+      <c r="F82" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G82" s="13" t="n">
+        <v>500</v>
+      </c>
+      <c r="H82" s="13" t="inlineStr">
+        <is>
+          <t>13 ms</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="13" t="inlineStr">
+        <is>
+          <t>500 VUs</t>
+        </is>
+      </c>
+      <c r="B83" s="13" t="inlineStr">
+        <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="C83" s="12" t="inlineStr">
+        <is>
+          <t>Upload Medical Record</t>
+        </is>
+      </c>
+      <c r="D83" s="13" t="inlineStr">
+        <is>
+          <t>360 MB</t>
+        </is>
+      </c>
+      <c r="E83" s="13" t="inlineStr">
+        <is>
+          <t>45.0%</t>
+        </is>
+      </c>
+      <c r="F83" s="13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="G83" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H83" s="13" t="inlineStr">
+        <is>
+          <t>13 ms</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="13" t="inlineStr">
+        <is>
+          <t>500 VUs</t>
+        </is>
+      </c>
+      <c r="B84" s="13" t="inlineStr">
+        <is>
+          <t>S13</t>
+        </is>
+      </c>
+      <c r="C84" s="12" t="inlineStr">
+        <is>
+          <t>Patient Dashboard Loading</t>
+        </is>
+      </c>
+      <c r="D84" s="13" t="inlineStr">
+        <is>
+          <t>350 MB</t>
+        </is>
+      </c>
+      <c r="E84" s="13" t="inlineStr">
+        <is>
+          <t>46.5%</t>
+        </is>
+      </c>
+      <c r="F84" s="13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="G84" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H84" s="13" t="inlineStr">
+        <is>
+          <t>13 ms</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="13" t="inlineStr">
+        <is>
+          <t>500 VUs</t>
+        </is>
+      </c>
+      <c r="B85" s="13" t="inlineStr">
+        <is>
+          <t>S14</t>
+        </is>
+      </c>
+      <c r="C85" s="12" t="inlineStr">
+        <is>
+          <t>Doctor Dashboard Loading</t>
+        </is>
+      </c>
+      <c r="D85" s="13" t="inlineStr">
+        <is>
+          <t>350 MB</t>
+        </is>
+      </c>
+      <c r="E85" s="13" t="inlineStr">
+        <is>
+          <t>45.0%</t>
+        </is>
+      </c>
+      <c r="F85" s="13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="G85" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H85" s="13" t="inlineStr">
+        <is>
+          <t>13 ms</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="13" t="inlineStr">
+        <is>
+          <t>1000 VUs</t>
+        </is>
+      </c>
+      <c r="B86" s="13" t="inlineStr">
+        <is>
+          <t>S01</t>
+        </is>
+      </c>
+      <c r="C86" s="12" t="inlineStr">
+        <is>
+          <t>User Login</t>
+        </is>
+      </c>
+      <c r="D86" s="13" t="inlineStr">
+        <is>
+          <t>550 MB</t>
+        </is>
+      </c>
+      <c r="E86" s="13" t="inlineStr">
+        <is>
+          <t>85.0%</t>
+        </is>
+      </c>
+      <c r="F86" s="13" t="n">
+        <v>2000</v>
+      </c>
+      <c r="G86" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H86" s="13" t="inlineStr">
+        <is>
+          <t>16 ms</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="13" t="inlineStr">
+        <is>
+          <t>1000 VUs</t>
+        </is>
+      </c>
+      <c r="B87" s="13" t="inlineStr">
+        <is>
+          <t>S02</t>
+        </is>
+      </c>
+      <c r="C87" s="12" t="inlineStr">
+        <is>
+          <t>User Registration</t>
+        </is>
+      </c>
+      <c r="D87" s="13" t="inlineStr">
+        <is>
+          <t>550 MB</t>
+        </is>
+      </c>
+      <c r="E87" s="13" t="inlineStr">
+        <is>
+          <t>85.0%</t>
+        </is>
+      </c>
+      <c r="F87" s="13" t="n">
+        <v>2000</v>
+      </c>
+      <c r="G87" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H87" s="13" t="inlineStr">
+        <is>
+          <t>16 ms</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="13" t="inlineStr">
+        <is>
+          <t>1000 VUs</t>
+        </is>
+      </c>
+      <c r="B88" s="13" t="inlineStr">
+        <is>
+          <t>S03</t>
+        </is>
+      </c>
+      <c r="C88" s="12" t="inlineStr">
+        <is>
+          <t>Update Doctor Profile</t>
+        </is>
+      </c>
+      <c r="D88" s="13" t="inlineStr">
+        <is>
+          <t>550 MB</t>
+        </is>
+      </c>
+      <c r="E88" s="13" t="inlineStr">
+        <is>
+          <t>85.0%</t>
+        </is>
+      </c>
+      <c r="F88" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G88" s="13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H88" s="13" t="inlineStr">
+        <is>
+          <t>16 ms</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="13" t="inlineStr">
+        <is>
+          <t>1000 VUs</t>
+        </is>
+      </c>
+      <c r="B89" s="13" t="inlineStr">
+        <is>
+          <t>S04</t>
+        </is>
+      </c>
+      <c r="C89" s="12" t="inlineStr">
+        <is>
+          <t>Book Appointment</t>
+        </is>
+      </c>
+      <c r="D89" s="13" t="inlineStr">
+        <is>
+          <t>550 MB</t>
+        </is>
+      </c>
+      <c r="E89" s="13" t="inlineStr">
+        <is>
+          <t>85.0%</t>
+        </is>
+      </c>
+      <c r="F89" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G89" s="13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H89" s="13" t="inlineStr">
+        <is>
+          <t>16 ms</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="13" t="inlineStr">
+        <is>
+          <t>1000 VUs</t>
+        </is>
+      </c>
+      <c r="B90" s="13" t="inlineStr">
+        <is>
+          <t>S05</t>
+        </is>
+      </c>
+      <c r="C90" s="12" t="inlineStr">
+        <is>
+          <t>Patient Appointments List</t>
+        </is>
+      </c>
+      <c r="D90" s="13" t="inlineStr">
+        <is>
+          <t>550 MB</t>
+        </is>
+      </c>
+      <c r="E90" s="13" t="inlineStr">
+        <is>
+          <t>85.0%</t>
+        </is>
+      </c>
+      <c r="F90" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G90" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H90" s="13" t="inlineStr">
+        <is>
+          <t>16 ms</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="13" t="inlineStr">
+        <is>
+          <t>1000 VUs</t>
+        </is>
+      </c>
+      <c r="B91" s="13" t="inlineStr">
+        <is>
+          <t>S06</t>
+        </is>
+      </c>
+      <c r="C91" s="12" t="inlineStr">
+        <is>
+          <t>Doctor Appointments List</t>
+        </is>
+      </c>
+      <c r="D91" s="13" t="inlineStr">
+        <is>
+          <t>550 MB</t>
+        </is>
+      </c>
+      <c r="E91" s="13" t="inlineStr">
+        <is>
+          <t>85.0%</t>
+        </is>
+      </c>
+      <c r="F91" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G91" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H91" s="13" t="inlineStr">
+        <is>
+          <t>16 ms</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="13" t="inlineStr">
+        <is>
+          <t>1000 VUs</t>
+        </is>
+      </c>
+      <c r="B92" s="13" t="inlineStr">
+        <is>
+          <t>S07</t>
+        </is>
+      </c>
+      <c r="C92" s="12" t="inlineStr">
+        <is>
+          <t>Get Appointment Details</t>
+        </is>
+      </c>
+      <c r="D92" s="13" t="inlineStr">
+        <is>
+          <t>550 MB</t>
+        </is>
+      </c>
+      <c r="E92" s="13" t="inlineStr">
+        <is>
+          <t>85.0%</t>
+        </is>
+      </c>
+      <c r="F92" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G92" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H92" s="13" t="inlineStr">
+        <is>
+          <t>16 ms</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="13" t="inlineStr">
+        <is>
+          <t>1000 VUs</t>
+        </is>
+      </c>
+      <c r="B93" s="13" t="inlineStr">
+        <is>
+          <t>S08</t>
+        </is>
+      </c>
+      <c r="C93" s="12" t="inlineStr">
+        <is>
+          <t>Queue Registration</t>
+        </is>
+      </c>
+      <c r="D93" s="13" t="inlineStr">
+        <is>
+          <t>550 MB</t>
+        </is>
+      </c>
+      <c r="E93" s="13" t="inlineStr">
+        <is>
+          <t>85.0%</t>
+        </is>
+      </c>
+      <c r="F93" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G93" s="13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H93" s="13" t="inlineStr">
+        <is>
+          <t>16 ms</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="13" t="inlineStr">
+        <is>
+          <t>1000 VUs</t>
+        </is>
+      </c>
+      <c r="B94" s="13" t="inlineStr">
+        <is>
+          <t>S09</t>
+        </is>
+      </c>
+      <c r="C94" s="12" t="inlineStr">
+        <is>
+          <t>Update Queue Status</t>
+        </is>
+      </c>
+      <c r="D94" s="13" t="inlineStr">
+        <is>
+          <t>550 MB</t>
+        </is>
+      </c>
+      <c r="E94" s="13" t="inlineStr">
+        <is>
+          <t>85.0%</t>
+        </is>
+      </c>
+      <c r="F94" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G94" s="13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H94" s="13" t="inlineStr">
+        <is>
+          <t>16 ms</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="13" t="inlineStr">
+        <is>
+          <t>1000 VUs</t>
+        </is>
+      </c>
+      <c r="B95" s="13" t="inlineStr">
+        <is>
+          <t>S10</t>
+        </is>
+      </c>
+      <c r="C95" s="12" t="inlineStr">
+        <is>
+          <t>Fetch Notifications</t>
+        </is>
+      </c>
+      <c r="D95" s="13" t="inlineStr">
+        <is>
+          <t>550 MB</t>
+        </is>
+      </c>
+      <c r="E95" s="13" t="inlineStr">
+        <is>
+          <t>85.0%</t>
+        </is>
+      </c>
+      <c r="F95" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G95" s="13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H95" s="13" t="inlineStr">
+        <is>
+          <t>16 ms</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="13" t="inlineStr">
+        <is>
+          <t>1000 VUs</t>
+        </is>
+      </c>
+      <c r="B96" s="13" t="inlineStr">
+        <is>
+          <t>S11</t>
+        </is>
+      </c>
+      <c r="C96" s="12" t="inlineStr">
+        <is>
+          <t>Submit Feedback</t>
+        </is>
+      </c>
+      <c r="D96" s="13" t="inlineStr">
+        <is>
+          <t>550 MB</t>
+        </is>
+      </c>
+      <c r="E96" s="13" t="inlineStr">
+        <is>
+          <t>85.0%</t>
+        </is>
+      </c>
+      <c r="F96" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G96" s="13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H96" s="13" t="inlineStr">
+        <is>
+          <t>16 ms</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="13" t="inlineStr">
+        <is>
+          <t>1000 VUs</t>
+        </is>
+      </c>
+      <c r="B97" s="13" t="inlineStr">
+        <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="C97" s="12" t="inlineStr">
+        <is>
+          <t>Upload Medical Record</t>
+        </is>
+      </c>
+      <c r="D97" s="13" t="inlineStr">
+        <is>
+          <t>560 MB</t>
+        </is>
+      </c>
+      <c r="E97" s="13" t="inlineStr">
+        <is>
+          <t>85.0%</t>
+        </is>
+      </c>
+      <c r="F97" s="13" t="n">
+        <v>2000</v>
+      </c>
+      <c r="G97" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H97" s="13" t="inlineStr">
+        <is>
+          <t>16 ms</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="13" t="inlineStr">
+        <is>
+          <t>1000 VUs</t>
+        </is>
+      </c>
+      <c r="B98" s="13" t="inlineStr">
+        <is>
+          <t>S13</t>
+        </is>
+      </c>
+      <c r="C98" s="12" t="inlineStr">
+        <is>
+          <t>Patient Dashboard Loading</t>
+        </is>
+      </c>
+      <c r="D98" s="13" t="inlineStr">
+        <is>
+          <t>550 MB</t>
+        </is>
+      </c>
+      <c r="E98" s="13" t="inlineStr">
+        <is>
+          <t>86.5%</t>
+        </is>
+      </c>
+      <c r="F98" s="13" t="n">
+        <v>2000</v>
+      </c>
+      <c r="G98" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H98" s="13" t="inlineStr">
+        <is>
+          <t>16 ms</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="13" t="inlineStr">
+        <is>
+          <t>1000 VUs</t>
+        </is>
+      </c>
+      <c r="B99" s="13" t="inlineStr">
+        <is>
+          <t>S14</t>
+        </is>
+      </c>
+      <c r="C99" s="12" t="inlineStr">
+        <is>
+          <t>Doctor Dashboard Loading</t>
+        </is>
+      </c>
+      <c r="D99" s="13" t="inlineStr">
+        <is>
+          <t>550 MB</t>
+        </is>
+      </c>
+      <c r="E99" s="13" t="inlineStr">
+        <is>
+          <t>85.0%</t>
+        </is>
+      </c>
+      <c r="F99" s="13" t="n">
+        <v>2000</v>
+      </c>
+      <c r="G99" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H99" s="13" t="inlineStr">
+        <is>
+          <t>16 ms</t>
         </is>
       </c>
     </row>
